--- a/research/traditional_assets/database/data/latvia/latvia_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_retail_automotive.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08795261237111254</v>
+        <v>0.08781270714637031</v>
       </c>
       <c r="C2">
-        <v>103.5733513380512</v>
+        <v>102.8762097756671</v>
       </c>
       <c r="D2">
-        <v>97.85335133805117</v>
+        <v>98.17920977566708</v>
       </c>
       <c r="E2">
-        <v>-37.7</v>
+        <v>-36.677</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.023</v>
       </c>
       <c r="G2">
         <v>5.72</v>
@@ -1439,28 +1439,28 @@
         <v>12.22</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05145689999999999</v>
       </c>
       <c r="N2">
-        <v>12.22</v>
+        <v>12.1685431</v>
       </c>
       <c r="O2">
-        <v>2.444</v>
+        <v>2.43370862</v>
       </c>
       <c r="P2">
-        <v>9.776</v>
+        <v>9.73483448</v>
       </c>
       <c r="Q2">
-        <v>15.156</v>
+        <v>15.11483448</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08795261237111254</v>
+        <v>0.08829323954178819</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307609</v>
+        <v>0.7164970653807065</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>237.4802990463864</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08781270714637031</v>
+        <v>0.08767280192162807</v>
       </c>
       <c r="C3">
-        <v>102.8762097756671</v>
+        <v>102.1812457268888</v>
       </c>
       <c r="D3">
-        <v>98.17920977566708</v>
+        <v>98.50724572688878</v>
       </c>
       <c r="E3">
-        <v>-36.677</v>
+        <v>-35.654</v>
       </c>
       <c r="F3">
-        <v>1.023</v>
+        <v>2.046</v>
       </c>
       <c r="G3">
         <v>5.72</v>
@@ -1521,28 +1521,28 @@
         <v>12.22</v>
       </c>
       <c r="M3">
-        <v>0.05145689999999999</v>
+        <v>0.1029138</v>
       </c>
       <c r="N3">
-        <v>12.1685431</v>
+        <v>12.1170862</v>
       </c>
       <c r="O3">
-        <v>2.43370862</v>
+        <v>2.42341724</v>
       </c>
       <c r="P3">
-        <v>9.73483448</v>
+        <v>9.69366896</v>
       </c>
       <c r="Q3">
-        <v>15.11483448</v>
+        <v>15.07366896</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08829323954178819</v>
+        <v>0.08864081828737559</v>
       </c>
       <c r="T3">
-        <v>0.7164970653807065</v>
+        <v>0.7223577423704467</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>237.4802990463864</v>
+        <v>118.7401495231932</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08767280192162807</v>
+        <v>0.08753289669688585</v>
       </c>
       <c r="C4">
-        <v>102.1812457268888</v>
+        <v>101.4884810913845</v>
       </c>
       <c r="D4">
-        <v>98.50724572688878</v>
+        <v>98.83748109138449</v>
       </c>
       <c r="E4">
-        <v>-35.654</v>
+        <v>-34.631</v>
       </c>
       <c r="F4">
-        <v>2.046</v>
+        <v>3.069</v>
       </c>
       <c r="G4">
         <v>5.72</v>
@@ -1603,28 +1603,28 @@
         <v>12.22</v>
       </c>
       <c r="M4">
-        <v>0.1029138</v>
+        <v>0.1543707</v>
       </c>
       <c r="N4">
-        <v>12.1170862</v>
+        <v>12.0656293</v>
       </c>
       <c r="O4">
-        <v>2.42341724</v>
+        <v>2.41312586</v>
       </c>
       <c r="P4">
-        <v>9.69366896</v>
+        <v>9.65250344</v>
       </c>
       <c r="Q4">
-        <v>15.07366896</v>
+        <v>15.03250344</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08864081828737559</v>
+        <v>0.08899556360503696</v>
       </c>
       <c r="T4">
-        <v>0.7223577423704467</v>
+        <v>0.7283392580610064</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>118.7401495231932</v>
+        <v>79.16009968212879</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08753289669688585</v>
+        <v>0.08739299147214363</v>
       </c>
       <c r="C5">
-        <v>101.4884810913845</v>
+        <v>100.7979380634757</v>
       </c>
       <c r="D5">
-        <v>98.83748109138449</v>
+        <v>99.16993806347571</v>
       </c>
       <c r="E5">
-        <v>-34.631</v>
+        <v>-33.608</v>
       </c>
       <c r="F5">
-        <v>3.069</v>
+        <v>4.092</v>
       </c>
       <c r="G5">
         <v>5.72</v>
@@ -1685,28 +1685,28 @@
         <v>12.22</v>
       </c>
       <c r="M5">
-        <v>0.1543707</v>
+        <v>0.2058276</v>
       </c>
       <c r="N5">
-        <v>12.0656293</v>
+        <v>12.0141724</v>
       </c>
       <c r="O5">
-        <v>2.41312586</v>
+        <v>2.40283448</v>
       </c>
       <c r="P5">
-        <v>9.65250344</v>
+        <v>9.61133792</v>
       </c>
       <c r="Q5">
-        <v>15.03250344</v>
+        <v>14.99133792</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08899556360503696</v>
+        <v>0.08935769945014962</v>
       </c>
       <c r="T5">
-        <v>0.7283392580610064</v>
+        <v>0.7344453886617863</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>79.16009968212879</v>
+        <v>59.37007476159661</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08739299147214363</v>
+        <v>0.08725308624740141</v>
       </c>
       <c r="C6">
-        <v>100.7979380634757</v>
+        <v>100.1096391371096</v>
       </c>
       <c r="D6">
-        <v>99.16993806347571</v>
+        <v>99.50463913710959</v>
       </c>
       <c r="E6">
-        <v>-33.608</v>
+        <v>-32.585</v>
       </c>
       <c r="F6">
-        <v>4.092</v>
+        <v>5.115</v>
       </c>
       <c r="G6">
         <v>5.72</v>
@@ -1767,28 +1767,28 @@
         <v>12.22</v>
       </c>
       <c r="M6">
-        <v>0.2058276</v>
+        <v>0.2572845</v>
       </c>
       <c r="N6">
-        <v>12.0141724</v>
+        <v>11.9627155</v>
       </c>
       <c r="O6">
-        <v>2.40283448</v>
+        <v>2.3925431</v>
       </c>
       <c r="P6">
-        <v>9.61133792</v>
+        <v>9.570172399999999</v>
       </c>
       <c r="Q6">
-        <v>14.99133792</v>
+        <v>14.9501724</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08935769945014962</v>
+        <v>0.08972745920779096</v>
       </c>
       <c r="T6">
-        <v>0.7344453886617863</v>
+        <v>0.740680069380477</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>59.37007476159661</v>
+        <v>47.49605980927728</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08725308624740141</v>
+        <v>0.08711318102265918</v>
       </c>
       <c r="C7">
-        <v>100.1096391371096</v>
+        <v>99.4236071109322</v>
       </c>
       <c r="D7">
-        <v>99.50463913710959</v>
+        <v>99.8416071109322</v>
       </c>
       <c r="E7">
-        <v>-32.585</v>
+        <v>-31.562</v>
       </c>
       <c r="F7">
-        <v>5.115</v>
+        <v>6.138</v>
       </c>
       <c r="G7">
         <v>5.72</v>
@@ -1849,28 +1849,28 @@
         <v>12.22</v>
       </c>
       <c r="M7">
-        <v>0.2572845</v>
+        <v>0.3087414</v>
       </c>
       <c r="N7">
-        <v>11.9627155</v>
+        <v>11.9112586</v>
       </c>
       <c r="O7">
-        <v>2.3925431</v>
+        <v>2.38225172</v>
       </c>
       <c r="P7">
-        <v>9.570172399999999</v>
+        <v>9.529006879999999</v>
       </c>
       <c r="Q7">
-        <v>14.9501724</v>
+        <v>14.90900688</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08972745920779096</v>
+        <v>0.09010508619431828</v>
       </c>
       <c r="T7">
-        <v>0.740680069380477</v>
+        <v>0.7470474028804168</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>47.49605980927728</v>
+        <v>39.58004984106439</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08711318102265918</v>
+        <v>0.08697327579791696</v>
       </c>
       <c r="C8">
-        <v>99.4236071109322</v>
+        <v>98.7398650934653</v>
       </c>
       <c r="D8">
-        <v>99.8416071109322</v>
+        <v>100.1808650934653</v>
       </c>
       <c r="E8">
-        <v>-31.562</v>
+        <v>-30.53900000000001</v>
       </c>
       <c r="F8">
-        <v>6.138</v>
+        <v>7.160999999999999</v>
       </c>
       <c r="G8">
         <v>5.72</v>
@@ -1931,28 +1931,28 @@
         <v>12.22</v>
       </c>
       <c r="M8">
-        <v>0.3087414</v>
+        <v>0.3601982999999999</v>
       </c>
       <c r="N8">
-        <v>11.9112586</v>
+        <v>11.8598017</v>
       </c>
       <c r="O8">
-        <v>2.38225172</v>
+        <v>2.37196034</v>
       </c>
       <c r="P8">
-        <v>9.529006879999999</v>
+        <v>9.487841359999999</v>
       </c>
       <c r="Q8">
-        <v>14.90900688</v>
+        <v>14.86784136</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09010508619431828</v>
+        <v>0.09049083419130856</v>
       </c>
       <c r="T8">
-        <v>0.7470474028804168</v>
+        <v>0.7535516682835809</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.58004984106439</v>
+        <v>33.92575700662663</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08697327579791694</v>
+        <v>0.08683337057317474</v>
       </c>
       <c r="C9">
-        <v>98.73986509346531</v>
+        <v>98.05843650838908</v>
       </c>
       <c r="D9">
-        <v>100.1808650934653</v>
+        <v>100.5224365083891</v>
       </c>
       <c r="E9">
-        <v>-30.539</v>
+        <v>-29.51600000000001</v>
       </c>
       <c r="F9">
-        <v>7.161</v>
+        <v>8.183999999999999</v>
       </c>
       <c r="G9">
         <v>5.72</v>
@@ -2013,28 +2013,28 @@
         <v>12.22</v>
       </c>
       <c r="M9">
-        <v>0.3601983</v>
+        <v>0.4116551999999999</v>
       </c>
       <c r="N9">
-        <v>11.8598017</v>
+        <v>11.8083448</v>
       </c>
       <c r="O9">
-        <v>2.37196034</v>
+        <v>2.36166896</v>
       </c>
       <c r="P9">
-        <v>9.487841359999999</v>
+        <v>9.446675839999999</v>
       </c>
       <c r="Q9">
-        <v>14.86784136</v>
+        <v>14.82667584</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09049083419130856</v>
+        <v>0.09088496801432036</v>
       </c>
       <c r="T9">
-        <v>0.7535516682835809</v>
+        <v>0.7601973307607268</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.92575700662662</v>
+        <v>29.6850373807983</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08683337057317474</v>
+        <v>0.0866934653484325</v>
       </c>
       <c r="C10">
-        <v>98.05843650838908</v>
+        <v>97.37934509993333</v>
       </c>
       <c r="D10">
-        <v>100.5224365083891</v>
+        <v>100.8663450999333</v>
       </c>
       <c r="E10">
-        <v>-29.51600000000001</v>
+        <v>-28.493</v>
       </c>
       <c r="F10">
-        <v>8.183999999999999</v>
+        <v>9.206999999999999</v>
       </c>
       <c r="G10">
         <v>5.72</v>
@@ -2095,28 +2095,28 @@
         <v>12.22</v>
       </c>
       <c r="M10">
-        <v>0.4116551999999999</v>
+        <v>0.4631120999999999</v>
       </c>
       <c r="N10">
-        <v>11.8083448</v>
+        <v>11.7568879</v>
       </c>
       <c r="O10">
-        <v>2.36166896</v>
+        <v>2.35137758</v>
       </c>
       <c r="P10">
-        <v>9.446675839999999</v>
+        <v>9.405510319999999</v>
       </c>
       <c r="Q10">
-        <v>14.82667584</v>
+        <v>14.78551032</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09088496801432036</v>
+        <v>0.09128776411915659</v>
       </c>
       <c r="T10">
-        <v>0.7601973307607268</v>
+        <v>0.766989051753854</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.6850373807983</v>
+        <v>26.38669989404293</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0866934653484325</v>
+        <v>0.08655356012369028</v>
       </c>
       <c r="C11">
-        <v>97.37934509993333</v>
+        <v>96.7026149383794</v>
       </c>
       <c r="D11">
-        <v>100.8663450999333</v>
+        <v>101.2126149383794</v>
       </c>
       <c r="E11">
-        <v>-28.493</v>
+        <v>-27.47000000000001</v>
       </c>
       <c r="F11">
-        <v>9.206999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G11">
         <v>5.72</v>
@@ -2177,28 +2177,28 @@
         <v>12.22</v>
       </c>
       <c r="M11">
-        <v>0.4631120999999999</v>
+        <v>0.5145689999999999</v>
       </c>
       <c r="N11">
-        <v>11.7568879</v>
+        <v>11.705431</v>
       </c>
       <c r="O11">
-        <v>2.35137758</v>
+        <v>2.3410862</v>
       </c>
       <c r="P11">
-        <v>9.405510319999999</v>
+        <v>9.3643448</v>
       </c>
       <c r="Q11">
-        <v>14.78551032</v>
+        <v>14.7443448</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09128776411915659</v>
+        <v>0.09169951124854475</v>
       </c>
       <c r="T11">
-        <v>0.766989051753854</v>
+        <v>0.7739316998801617</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.38669989404293</v>
+        <v>23.74802990463864</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08655356012369031</v>
+        <v>0.08641365489894805</v>
       </c>
       <c r="C12">
-        <v>96.70261493837933</v>
+        <v>96.02827042567637</v>
       </c>
       <c r="D12">
-        <v>101.2126149383793</v>
+        <v>101.5612704256764</v>
       </c>
       <c r="E12">
-        <v>-27.47</v>
+        <v>-26.447</v>
       </c>
       <c r="F12">
-        <v>10.23</v>
+        <v>11.253</v>
       </c>
       <c r="G12">
         <v>5.72</v>
@@ -2259,28 +2259,28 @@
         <v>12.22</v>
       </c>
       <c r="M12">
-        <v>0.5145689999999999</v>
+        <v>0.5660259</v>
       </c>
       <c r="N12">
-        <v>11.705431</v>
+        <v>11.6539741</v>
       </c>
       <c r="O12">
-        <v>2.3410862</v>
+        <v>2.33079482</v>
       </c>
       <c r="P12">
-        <v>9.3643448</v>
+        <v>9.32317928</v>
       </c>
       <c r="Q12">
-        <v>14.7443448</v>
+        <v>14.70317928</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09169951124854478</v>
+        <v>0.09212051112241354</v>
       </c>
       <c r="T12">
-        <v>0.773931699880162</v>
+        <v>0.7810303625711057</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.74802990463864</v>
+        <v>21.58911809512604</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08641365489894805</v>
+        <v>0.08627374967420583</v>
       </c>
       <c r="C13">
-        <v>96.02827042567637</v>
+        <v>95.35633630117306</v>
       </c>
       <c r="D13">
-        <v>101.5612704256764</v>
+        <v>101.9123363011731</v>
       </c>
       <c r="E13">
-        <v>-26.447</v>
+        <v>-25.424</v>
       </c>
       <c r="F13">
-        <v>11.253</v>
+        <v>12.276</v>
       </c>
       <c r="G13">
         <v>5.72</v>
@@ -2341,28 +2341,28 @@
         <v>12.22</v>
       </c>
       <c r="M13">
-        <v>0.5660259</v>
+        <v>0.6174828</v>
       </c>
       <c r="N13">
-        <v>11.6539741</v>
+        <v>11.6025172</v>
       </c>
       <c r="O13">
-        <v>2.33079482</v>
+        <v>2.32050344</v>
       </c>
       <c r="P13">
-        <v>9.32317928</v>
+        <v>9.28201376</v>
       </c>
       <c r="Q13">
-        <v>14.70317928</v>
+        <v>14.66201376</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09212051112241354</v>
+        <v>0.09255107917523391</v>
       </c>
       <c r="T13">
-        <v>0.7810303625711057</v>
+        <v>0.7882903585050257</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.58911809512604</v>
+        <v>19.7900249205322</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08627374967420583</v>
+        <v>0.08613384444946361</v>
       </c>
       <c r="C14">
-        <v>95.35633630117306</v>
+        <v>94.6868376474701</v>
       </c>
       <c r="D14">
-        <v>101.9123363011731</v>
+        <v>102.2658376474701</v>
       </c>
       <c r="E14">
-        <v>-25.424</v>
+        <v>-24.401</v>
       </c>
       <c r="F14">
-        <v>12.276</v>
+        <v>13.299</v>
       </c>
       <c r="G14">
         <v>5.72</v>
@@ -2423,28 +2423,28 @@
         <v>12.22</v>
       </c>
       <c r="M14">
-        <v>0.6174828</v>
+        <v>0.6689396999999999</v>
       </c>
       <c r="N14">
-        <v>11.6025172</v>
+        <v>11.5510603</v>
       </c>
       <c r="O14">
-        <v>2.32050344</v>
+        <v>2.31021206</v>
       </c>
       <c r="P14">
-        <v>9.28201376</v>
+        <v>9.24084824</v>
       </c>
       <c r="Q14">
-        <v>14.66201376</v>
+        <v>14.62084824</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09255107917523391</v>
+        <v>0.09299154534421104</v>
       </c>
       <c r="T14">
-        <v>0.7882903585050257</v>
+        <v>0.7957172508971966</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.7900249205322</v>
+        <v>18.26771531126049</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08613384444946361</v>
+        <v>0.08599393922472139</v>
       </c>
       <c r="C15">
-        <v>94.6868376474701</v>
+        <v>94.01979989639347</v>
       </c>
       <c r="D15">
-        <v>102.2658376474701</v>
+        <v>102.6217998963935</v>
       </c>
       <c r="E15">
-        <v>-24.401</v>
+        <v>-23.378</v>
       </c>
       <c r="F15">
-        <v>13.299</v>
+        <v>14.322</v>
       </c>
       <c r="G15">
         <v>5.72</v>
@@ -2505,28 +2505,28 @@
         <v>12.22</v>
       </c>
       <c r="M15">
-        <v>0.6689396999999999</v>
+        <v>0.7203966000000001</v>
       </c>
       <c r="N15">
-        <v>11.5510603</v>
+        <v>11.4996034</v>
       </c>
       <c r="O15">
-        <v>2.31021206</v>
+        <v>2.29992068</v>
       </c>
       <c r="P15">
-        <v>9.24084824</v>
+        <v>9.199682719999998</v>
       </c>
       <c r="Q15">
-        <v>14.62084824</v>
+        <v>14.57968272</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09299154534421104</v>
+        <v>0.09344225491246673</v>
       </c>
       <c r="T15">
-        <v>0.7957172508971966</v>
+        <v>0.8033168617170926</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.26771531126049</v>
+        <v>16.96287850331331</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08599393922472139</v>
+        <v>0.08585403399997917</v>
       </c>
       <c r="C16">
-        <v>94.01979989639347</v>
+        <v>93.35524883509372</v>
       </c>
       <c r="D16">
-        <v>102.6217998963935</v>
+        <v>102.9802488350937</v>
       </c>
       <c r="E16">
-        <v>-23.378</v>
+        <v>-22.355</v>
       </c>
       <c r="F16">
-        <v>14.322</v>
+        <v>15.345</v>
       </c>
       <c r="G16">
         <v>5.72</v>
@@ -2587,28 +2587,28 @@
         <v>12.22</v>
       </c>
       <c r="M16">
-        <v>0.7203966000000001</v>
+        <v>0.7718535000000001</v>
       </c>
       <c r="N16">
-        <v>11.4996034</v>
+        <v>11.4481465</v>
       </c>
       <c r="O16">
-        <v>2.29992068</v>
+        <v>2.2896293</v>
       </c>
       <c r="P16">
-        <v>9.199682719999998</v>
+        <v>9.158517199999999</v>
       </c>
       <c r="Q16">
-        <v>14.57968272</v>
+        <v>14.5385172</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09344225491246673</v>
+        <v>0.09390356941174019</v>
       </c>
       <c r="T16">
-        <v>0.8033168617170926</v>
+        <v>0.8110952869092212</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.96287850331331</v>
+        <v>15.83201993642576</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08585403399997917</v>
+        <v>0.08571412877523693</v>
       </c>
       <c r="C17">
-        <v>93.35524883509372</v>
+        <v>92.6932106122733</v>
       </c>
       <c r="D17">
-        <v>102.9802488350937</v>
+        <v>103.3412106122733</v>
       </c>
       <c r="E17">
-        <v>-22.355</v>
+        <v>-21.332</v>
       </c>
       <c r="F17">
-        <v>15.345</v>
+        <v>16.368</v>
       </c>
       <c r="G17">
         <v>5.72</v>
@@ -2669,28 +2669,28 @@
         <v>12.22</v>
       </c>
       <c r="M17">
-        <v>0.7718534999999999</v>
+        <v>0.8233103999999999</v>
       </c>
       <c r="N17">
-        <v>11.4481465</v>
+        <v>11.3966896</v>
       </c>
       <c r="O17">
-        <v>2.2896293</v>
+        <v>2.27933792</v>
       </c>
       <c r="P17">
-        <v>9.158517199999999</v>
+        <v>9.117351679999999</v>
       </c>
       <c r="Q17">
-        <v>14.5385172</v>
+        <v>14.49735168</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09390356941174019</v>
+        <v>0.09437586758956779</v>
       </c>
       <c r="T17">
-        <v>0.8110952869092212</v>
+        <v>0.8190589127011625</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.83201993642576</v>
+        <v>14.84251869039915</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08571412877523693</v>
+        <v>0.08557422355049471</v>
       </c>
       <c r="C18">
-        <v>92.6932106122733</v>
+        <v>92.03371174454527</v>
       </c>
       <c r="D18">
-        <v>103.3412106122733</v>
+        <v>103.7047117445453</v>
       </c>
       <c r="E18">
-        <v>-21.332</v>
+        <v>-20.309</v>
       </c>
       <c r="F18">
-        <v>16.368</v>
+        <v>17.391</v>
       </c>
       <c r="G18">
         <v>5.72</v>
@@ -2751,28 +2751,28 @@
         <v>12.22</v>
       </c>
       <c r="M18">
-        <v>0.8233103999999999</v>
+        <v>0.8747673</v>
       </c>
       <c r="N18">
-        <v>11.3966896</v>
+        <v>11.3452327</v>
       </c>
       <c r="O18">
-        <v>2.27933792</v>
+        <v>2.26904654</v>
       </c>
       <c r="P18">
-        <v>9.117351679999999</v>
+        <v>9.076186159999999</v>
       </c>
       <c r="Q18">
-        <v>14.49735168</v>
+        <v>14.45618616</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09437586758956779</v>
+        <v>0.09485954644637917</v>
       </c>
       <c r="T18">
-        <v>0.8190589127011625</v>
+        <v>0.8272144330904999</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.84251869039915</v>
+        <v>13.96942935566979</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08557422355049471</v>
+        <v>0.08543431832575249</v>
       </c>
       <c r="C19">
-        <v>92.03371174454527</v>
+        <v>91.37677912292683</v>
       </c>
       <c r="D19">
-        <v>103.7047117445453</v>
+        <v>104.0707791229268</v>
       </c>
       <c r="E19">
-        <v>-20.309</v>
+        <v>-19.286</v>
       </c>
       <c r="F19">
-        <v>17.391</v>
+        <v>18.414</v>
       </c>
       <c r="G19">
         <v>5.72</v>
@@ -2833,28 +2833,28 @@
         <v>12.22</v>
       </c>
       <c r="M19">
-        <v>0.8747673</v>
+        <v>0.9262242000000001</v>
       </c>
       <c r="N19">
-        <v>11.3452327</v>
+        <v>11.2937758</v>
       </c>
       <c r="O19">
-        <v>2.26904654</v>
+        <v>2.25875516</v>
       </c>
       <c r="P19">
-        <v>9.076186159999999</v>
+        <v>9.035020639999999</v>
       </c>
       <c r="Q19">
-        <v>14.45618616</v>
+        <v>14.41502064</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09485954644637917</v>
+        <v>0.09535502234847865</v>
       </c>
       <c r="T19">
-        <v>0.8272144330904999</v>
+        <v>0.8355688686112849</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.96942935566979</v>
+        <v>13.19334994702146</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0854343183257525</v>
+        <v>0.08552241310101028</v>
       </c>
       <c r="C20">
-        <v>91.37677912292678</v>
+        <v>90.1229751213063</v>
       </c>
       <c r="D20">
-        <v>104.0707791229268</v>
+        <v>103.8399751213063</v>
       </c>
       <c r="E20">
-        <v>-19.286</v>
+        <v>-18.263</v>
       </c>
       <c r="F20">
-        <v>18.414</v>
+        <v>19.437</v>
       </c>
       <c r="G20">
         <v>5.72</v>
@@ -2915,45 +2915,45 @@
         <v>12.22</v>
       </c>
       <c r="M20">
-        <v>0.9262241999999998</v>
+        <v>1.0068366</v>
       </c>
       <c r="N20">
-        <v>11.2937758</v>
+        <v>11.2131634</v>
       </c>
       <c r="O20">
-        <v>2.25875516</v>
+        <v>2.24263268</v>
       </c>
       <c r="P20">
-        <v>9.035020639999999</v>
+        <v>8.970530719999999</v>
       </c>
       <c r="Q20">
-        <v>14.41502064</v>
+        <v>14.35053072</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09535502234847865</v>
+        <v>0.09586273222346947</v>
       </c>
       <c r="T20">
-        <v>0.8355688686112847</v>
+        <v>0.8441295864906074</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.19334994702147</v>
+        <v>12.13702402157411</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08552241310101028</v>
+        <v>0.08539450787626805</v>
       </c>
       <c r="C21">
-        <v>90.1229751213063</v>
+        <v>89.43541748610653</v>
       </c>
       <c r="D21">
-        <v>103.8399751213063</v>
+        <v>104.1754174861065</v>
       </c>
       <c r="E21">
-        <v>-18.263</v>
+        <v>-17.24</v>
       </c>
       <c r="F21">
-        <v>19.437</v>
+        <v>20.46</v>
       </c>
       <c r="G21">
         <v>5.72</v>
@@ -2997,28 +2997,28 @@
         <v>12.22</v>
       </c>
       <c r="M21">
-        <v>1.0068366</v>
+        <v>1.059828</v>
       </c>
       <c r="N21">
-        <v>11.2131634</v>
+        <v>11.160172</v>
       </c>
       <c r="O21">
-        <v>2.24263268</v>
+        <v>2.2320344</v>
       </c>
       <c r="P21">
-        <v>8.970530719999999</v>
+        <v>8.928137599999999</v>
       </c>
       <c r="Q21">
-        <v>14.35053072</v>
+        <v>14.3081376</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09586273222346947</v>
+        <v>0.09638313484533505</v>
       </c>
       <c r="T21">
-        <v>0.8441295864906074</v>
+        <v>0.852904322316913</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.13702402157411</v>
+        <v>11.5301728204954</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08539450787626805</v>
+        <v>0.08526660265152582</v>
       </c>
       <c r="C22">
-        <v>89.43541748610653</v>
+        <v>88.75003408573706</v>
       </c>
       <c r="D22">
-        <v>104.1754174861065</v>
+        <v>104.5130340857371</v>
       </c>
       <c r="E22">
-        <v>-17.24</v>
+        <v>-16.217</v>
       </c>
       <c r="F22">
-        <v>20.46</v>
+        <v>21.483</v>
       </c>
       <c r="G22">
         <v>5.72</v>
@@ -3079,28 +3079,28 @@
         <v>12.22</v>
       </c>
       <c r="M22">
-        <v>1.059828</v>
+        <v>1.1128194</v>
       </c>
       <c r="N22">
-        <v>11.160172</v>
+        <v>11.1071806</v>
       </c>
       <c r="O22">
-        <v>2.2320344</v>
+        <v>2.22143612</v>
       </c>
       <c r="P22">
-        <v>8.928137599999999</v>
+        <v>8.88574448</v>
       </c>
       <c r="Q22">
-        <v>14.3081376</v>
+        <v>14.26574448</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09638313484533505</v>
+        <v>0.09691671221712128</v>
       </c>
       <c r="T22">
-        <v>0.852904322316913</v>
+        <v>0.8619012033540113</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.5301728204954</v>
+        <v>10.98111697190038</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08526660265152582</v>
+        <v>0.08513869742678359</v>
       </c>
       <c r="C23">
-        <v>88.75003408573707</v>
+        <v>88.06684612801699</v>
       </c>
       <c r="D23">
-        <v>104.5130340857371</v>
+        <v>104.852846128017</v>
       </c>
       <c r="E23">
-        <v>-16.21700000000001</v>
+        <v>-15.194</v>
       </c>
       <c r="F23">
-        <v>21.483</v>
+        <v>22.506</v>
       </c>
       <c r="G23">
         <v>5.72</v>
@@ -3161,28 +3161,28 @@
         <v>12.22</v>
       </c>
       <c r="M23">
-        <v>1.1128194</v>
+        <v>1.1658108</v>
       </c>
       <c r="N23">
-        <v>11.1071806</v>
+        <v>11.0541892</v>
       </c>
       <c r="O23">
-        <v>2.22143612</v>
+        <v>2.21083784</v>
       </c>
       <c r="P23">
-        <v>8.88574448</v>
+        <v>8.84335136</v>
       </c>
       <c r="Q23">
-        <v>14.26574448</v>
+        <v>14.22335136</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09691671221712128</v>
+        <v>0.09746397105997895</v>
       </c>
       <c r="T23">
-        <v>0.8619012033540113</v>
+        <v>0.8711287736484711</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.98111697190038</v>
+        <v>10.48197529135945</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08513869742678359</v>
+        <v>0.08501079220204137</v>
       </c>
       <c r="C24">
-        <v>88.06684612801699</v>
+        <v>87.38587509748443</v>
       </c>
       <c r="D24">
-        <v>104.852846128017</v>
+        <v>105.1948750974844</v>
       </c>
       <c r="E24">
-        <v>-15.194</v>
+        <v>-14.171</v>
       </c>
       <c r="F24">
-        <v>22.506</v>
+        <v>23.529</v>
       </c>
       <c r="G24">
         <v>5.72</v>
@@ -3243,28 +3243,28 @@
         <v>12.22</v>
       </c>
       <c r="M24">
-        <v>1.1658108</v>
+        <v>1.2188022</v>
       </c>
       <c r="N24">
-        <v>11.0541892</v>
+        <v>11.0011978</v>
       </c>
       <c r="O24">
-        <v>2.21083784</v>
+        <v>2.20023956</v>
       </c>
       <c r="P24">
-        <v>8.84335136</v>
+        <v>8.800958239999998</v>
       </c>
       <c r="Q24">
-        <v>14.22335136</v>
+        <v>14.18095824</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09746397105997895</v>
+        <v>0.09802544441823555</v>
       </c>
       <c r="T24">
-        <v>0.8711287736484711</v>
+        <v>0.8805960210934363</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.48197529135945</v>
+        <v>10.02623723521339</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08501079220204137</v>
+        <v>0.08520928697729914</v>
       </c>
       <c r="C25">
-        <v>87.38587509748443</v>
+        <v>85.83303467934206</v>
       </c>
       <c r="D25">
-        <v>105.1948750974844</v>
+        <v>104.6650346793421</v>
       </c>
       <c r="E25">
-        <v>-14.171</v>
+        <v>-13.148</v>
       </c>
       <c r="F25">
-        <v>23.529</v>
+        <v>24.552</v>
       </c>
       <c r="G25">
         <v>5.72</v>
@@ -3325,45 +3325,45 @@
         <v>12.22</v>
       </c>
       <c r="M25">
-        <v>1.2188022</v>
+        <v>1.313532</v>
       </c>
       <c r="N25">
-        <v>11.0011978</v>
+        <v>10.906468</v>
       </c>
       <c r="O25">
-        <v>2.20023956</v>
+        <v>2.1812936</v>
       </c>
       <c r="P25">
-        <v>8.800958239999998</v>
+        <v>8.725174399999998</v>
       </c>
       <c r="Q25">
-        <v>14.18095824</v>
+        <v>14.1051744</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09802544441823555</v>
+        <v>0.09860169339118308</v>
       </c>
       <c r="T25">
-        <v>0.8805960210934363</v>
+        <v>0.8903124066290584</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.02623723521339</v>
+        <v>9.303161247689435</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08520928697729914</v>
+        <v>0.08509498175255691</v>
       </c>
       <c r="C26">
-        <v>85.83303467934206</v>
+        <v>85.11449493808483</v>
       </c>
       <c r="D26">
-        <v>104.6650346793421</v>
+        <v>104.9694949380848</v>
       </c>
       <c r="E26">
-        <v>-13.148</v>
+        <v>-12.125</v>
       </c>
       <c r="F26">
-        <v>24.552</v>
+        <v>25.575</v>
       </c>
       <c r="G26">
         <v>5.72</v>
@@ -3407,28 +3407,28 @@
         <v>12.22</v>
       </c>
       <c r="M26">
-        <v>1.313532</v>
+        <v>1.3682625</v>
       </c>
       <c r="N26">
-        <v>10.906468</v>
+        <v>10.8517375</v>
       </c>
       <c r="O26">
-        <v>2.1812936</v>
+        <v>2.1703475</v>
       </c>
       <c r="P26">
-        <v>8.725174399999998</v>
+        <v>8.681389999999999</v>
       </c>
       <c r="Q26">
-        <v>14.1051744</v>
+        <v>14.06139</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09860169339118308</v>
+        <v>0.09919330900340921</v>
       </c>
       <c r="T26">
-        <v>0.8903124066290583</v>
+        <v>0.9002878957789637</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.303161247689435</v>
+        <v>8.931034797781859</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08509498175255691</v>
+        <v>0.08498067652781469</v>
       </c>
       <c r="C27">
-        <v>85.11449493808483</v>
+        <v>84.39773165407051</v>
       </c>
       <c r="D27">
-        <v>104.9694949380848</v>
+        <v>105.2757316540705</v>
       </c>
       <c r="E27">
-        <v>-12.125</v>
+        <v>-11.102</v>
       </c>
       <c r="F27">
-        <v>25.575</v>
+        <v>26.598</v>
       </c>
       <c r="G27">
         <v>5.72</v>
@@ -3489,28 +3489,28 @@
         <v>12.22</v>
       </c>
       <c r="M27">
-        <v>1.3682625</v>
+        <v>1.422993</v>
       </c>
       <c r="N27">
-        <v>10.8517375</v>
+        <v>10.797007</v>
       </c>
       <c r="O27">
-        <v>2.1703475</v>
+        <v>2.1594014</v>
       </c>
       <c r="P27">
-        <v>8.681389999999999</v>
+        <v>8.637605599999999</v>
       </c>
       <c r="Q27">
-        <v>14.06139</v>
+        <v>14.0176056</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09919330900340921</v>
+        <v>0.0998009142267766</v>
       </c>
       <c r="T27">
-        <v>0.9002878957789637</v>
+        <v>0.9105329927437315</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.931034797781859</v>
+        <v>8.587533459405632</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08498067652781469</v>
+        <v>0.08486637130307245</v>
       </c>
       <c r="C28">
-        <v>84.39773165407051</v>
+        <v>83.68276042063462</v>
       </c>
       <c r="D28">
-        <v>105.2757316540705</v>
+        <v>105.5837604206346</v>
       </c>
       <c r="E28">
-        <v>-11.102</v>
+        <v>-10.079</v>
       </c>
       <c r="F28">
-        <v>26.598</v>
+        <v>27.621</v>
       </c>
       <c r="G28">
         <v>5.72</v>
@@ -3571,28 +3571,28 @@
         <v>12.22</v>
       </c>
       <c r="M28">
-        <v>1.422993</v>
+        <v>1.4777235</v>
       </c>
       <c r="N28">
-        <v>10.797007</v>
+        <v>10.7422765</v>
       </c>
       <c r="O28">
-        <v>2.1594014</v>
+        <v>2.1484553</v>
       </c>
       <c r="P28">
-        <v>8.637605599999999</v>
+        <v>8.593821199999999</v>
       </c>
       <c r="Q28">
-        <v>14.0176056</v>
+        <v>13.9738212</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0998009142267766</v>
+        <v>0.1004251661685924</v>
       </c>
       <c r="T28">
-        <v>0.9105329927437315</v>
+        <v>0.9210587772965751</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.587533459405632</v>
+        <v>8.269476664612831</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08486637130307245</v>
+        <v>0.08475206607833022</v>
       </c>
       <c r="C29">
-        <v>83.68276042063462</v>
+        <v>82.96959701414784</v>
       </c>
       <c r="D29">
-        <v>105.5837604206346</v>
+        <v>105.8935970141478</v>
       </c>
       <c r="E29">
-        <v>-10.079</v>
+        <v>-9.056000000000001</v>
       </c>
       <c r="F29">
-        <v>27.621</v>
+        <v>28.644</v>
       </c>
       <c r="G29">
         <v>5.72</v>
@@ -3653,28 +3653,28 @@
         <v>12.22</v>
       </c>
       <c r="M29">
-        <v>1.4777235</v>
+        <v>1.532454</v>
       </c>
       <c r="N29">
-        <v>10.7422765</v>
+        <v>10.687546</v>
       </c>
       <c r="O29">
-        <v>2.1484553</v>
+        <v>2.1375092</v>
       </c>
       <c r="P29">
-        <v>8.593821199999999</v>
+        <v>8.550036799999999</v>
       </c>
       <c r="Q29">
-        <v>13.9738212</v>
+        <v>13.9300368</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1004251661685924</v>
+        <v>0.1010667584421253</v>
       </c>
       <c r="T29">
-        <v>0.9210587772965751</v>
+        <v>0.9318769447536642</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.269476664612831</v>
+        <v>7.97413821230523</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08475206607833022</v>
+        <v>0.08463776085358801</v>
       </c>
       <c r="C30">
-        <v>82.96959701414784</v>
+        <v>82.25825739670937</v>
       </c>
       <c r="D30">
-        <v>105.8935970141478</v>
+        <v>106.2052573967094</v>
       </c>
       <c r="E30">
-        <v>-9.056000000000001</v>
+        <v>-8.033000000000001</v>
       </c>
       <c r="F30">
-        <v>28.644</v>
+        <v>29.667</v>
       </c>
       <c r="G30">
         <v>5.72</v>
@@ -3735,28 +3735,28 @@
         <v>12.22</v>
       </c>
       <c r="M30">
-        <v>1.532454</v>
+        <v>1.5871845</v>
       </c>
       <c r="N30">
-        <v>10.687546</v>
+        <v>10.6328155</v>
       </c>
       <c r="O30">
-        <v>2.1375092</v>
+        <v>2.1265631</v>
       </c>
       <c r="P30">
-        <v>8.550036799999999</v>
+        <v>8.506252399999999</v>
       </c>
       <c r="Q30">
-        <v>13.9300368</v>
+        <v>13.8862524</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1010667584421253</v>
+        <v>0.1017264237374479</v>
       </c>
       <c r="T30">
-        <v>0.9318769447536642</v>
+        <v>0.9429998493222208</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.97413821230523</v>
+        <v>7.699167929122291</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08463776085358801</v>
+        <v>0.08471545562884578</v>
       </c>
       <c r="C31">
-        <v>82.25825739670937</v>
+        <v>81.0232184144775</v>
       </c>
       <c r="D31">
-        <v>106.2052573967094</v>
+        <v>105.9932184144775</v>
       </c>
       <c r="E31">
-        <v>-8.033000000000005</v>
+        <v>-7.010000000000005</v>
       </c>
       <c r="F31">
-        <v>29.667</v>
+        <v>30.69</v>
       </c>
       <c r="G31">
         <v>5.72</v>
@@ -3817,45 +3817,45 @@
         <v>12.22</v>
       </c>
       <c r="M31">
-        <v>1.5871845</v>
+        <v>1.666467</v>
       </c>
       <c r="N31">
-        <v>10.6328155</v>
+        <v>10.553533</v>
       </c>
       <c r="O31">
-        <v>2.1265631</v>
+        <v>2.1107066</v>
       </c>
       <c r="P31">
-        <v>8.506252399999999</v>
+        <v>8.442826399999998</v>
       </c>
       <c r="Q31">
-        <v>13.8862524</v>
+        <v>13.8228264</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1017264237374479</v>
+        <v>0.1024049366126368</v>
       </c>
       <c r="T31">
-        <v>0.9429998493222208</v>
+        <v>0.9544405511641647</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.699167929122292</v>
+        <v>7.332878478841764</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08471545562884578</v>
+        <v>0.08460755040410356</v>
       </c>
       <c r="C32">
-        <v>81.0232184144775</v>
+        <v>80.29493482752261</v>
       </c>
       <c r="D32">
-        <v>105.9932184144775</v>
+        <v>106.2879348275226</v>
       </c>
       <c r="E32">
-        <v>-7.010000000000005</v>
+        <v>-5.987000000000005</v>
       </c>
       <c r="F32">
-        <v>30.69</v>
+        <v>31.713</v>
       </c>
       <c r="G32">
         <v>5.72</v>
@@ -3899,28 +3899,28 @@
         <v>12.22</v>
       </c>
       <c r="M32">
-        <v>1.666467</v>
+        <v>1.7220159</v>
       </c>
       <c r="N32">
-        <v>10.553533</v>
+        <v>10.4979841</v>
       </c>
       <c r="O32">
-        <v>2.1107066</v>
+        <v>2.09959682</v>
       </c>
       <c r="P32">
-        <v>8.442826399999998</v>
+        <v>8.398387279999998</v>
       </c>
       <c r="Q32">
-        <v>13.8228264</v>
+        <v>13.77838728</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1024049366126368</v>
+        <v>0.1031031165276863</v>
       </c>
       <c r="T32">
-        <v>0.9544405511641647</v>
+        <v>0.9662128675522518</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.332878478841764</v>
+        <v>7.096334011782353</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08460755040410356</v>
+        <v>0.08449964517936133</v>
       </c>
       <c r="C33">
-        <v>80.29493482752261</v>
+        <v>79.56829474094806</v>
       </c>
       <c r="D33">
-        <v>106.2879348275226</v>
+        <v>106.5842947409481</v>
       </c>
       <c r="E33">
-        <v>-5.987000000000005</v>
+        <v>-4.964000000000006</v>
       </c>
       <c r="F33">
-        <v>31.713</v>
+        <v>32.736</v>
       </c>
       <c r="G33">
         <v>5.72</v>
@@ -3981,28 +3981,28 @@
         <v>12.22</v>
       </c>
       <c r="M33">
-        <v>1.7220159</v>
+        <v>1.7775648</v>
       </c>
       <c r="N33">
-        <v>10.4979841</v>
+        <v>10.4424352</v>
       </c>
       <c r="O33">
-        <v>2.09959682</v>
+        <v>2.08848704</v>
       </c>
       <c r="P33">
-        <v>8.398387279999998</v>
+        <v>8.353948159999998</v>
       </c>
       <c r="Q33">
-        <v>13.77838728</v>
+        <v>13.73394816</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1031031165276863</v>
+        <v>0.1038218311461196</v>
       </c>
       <c r="T33">
-        <v>0.9662128675522518</v>
+        <v>0.9783314285399884</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.096334011782353</v>
+        <v>6.874573573914154</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08449964517936133</v>
+        <v>0.08439173995461911</v>
       </c>
       <c r="C34">
-        <v>79.56829474094806</v>
+        <v>78.84331194078247</v>
       </c>
       <c r="D34">
-        <v>106.5842947409481</v>
+        <v>106.8823119407825</v>
       </c>
       <c r="E34">
-        <v>-4.964000000000006</v>
+        <v>-3.941000000000003</v>
       </c>
       <c r="F34">
-        <v>32.736</v>
+        <v>33.759</v>
       </c>
       <c r="G34">
         <v>5.72</v>
@@ -4063,28 +4063,28 @@
         <v>12.22</v>
       </c>
       <c r="M34">
-        <v>1.7775648</v>
+        <v>1.8331137</v>
       </c>
       <c r="N34">
-        <v>10.4424352</v>
+        <v>10.3868863</v>
       </c>
       <c r="O34">
-        <v>2.08848704</v>
+        <v>2.07737726</v>
       </c>
       <c r="P34">
-        <v>8.353948159999998</v>
+        <v>8.309509039999998</v>
       </c>
       <c r="Q34">
-        <v>13.73394816</v>
+        <v>13.68950904</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1038218311461196</v>
+        <v>0.1045619999322673</v>
       </c>
       <c r="T34">
-        <v>0.9783314285399884</v>
+        <v>0.9908117376169114</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.874573573914154</v>
+        <v>6.666253162583422</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08439173995461911</v>
+        <v>0.08428383472987688</v>
       </c>
       <c r="C35">
-        <v>78.84331194078247</v>
+        <v>78.1200003676737</v>
       </c>
       <c r="D35">
-        <v>106.8823119407825</v>
+        <v>107.1820003676737</v>
       </c>
       <c r="E35">
-        <v>-3.941000000000003</v>
+        <v>-2.917999999999999</v>
       </c>
       <c r="F35">
-        <v>33.759</v>
+        <v>34.782</v>
       </c>
       <c r="G35">
         <v>5.72</v>
@@ -4145,28 +4145,28 @@
         <v>12.22</v>
       </c>
       <c r="M35">
-        <v>1.8331137</v>
+        <v>1.8886626</v>
       </c>
       <c r="N35">
-        <v>10.3868863</v>
+        <v>10.3313374</v>
       </c>
       <c r="O35">
-        <v>2.07737726</v>
+        <v>2.06626748</v>
       </c>
       <c r="P35">
-        <v>8.309509039999998</v>
+        <v>8.265069919999998</v>
       </c>
       <c r="Q35">
-        <v>13.68950904</v>
+        <v>13.64506992</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1045619999322673</v>
+        <v>0.105324598075571</v>
       </c>
       <c r="T35">
-        <v>0.9908117376169114</v>
+        <v>1.003670237877984</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.666253162583422</v>
+        <v>6.470186893095674</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08428383472987688</v>
+        <v>0.08417592950513465</v>
       </c>
       <c r="C36">
-        <v>78.1200003676737</v>
+        <v>77.39837411906254</v>
       </c>
       <c r="D36">
-        <v>107.1820003676737</v>
+        <v>107.4833741190625</v>
       </c>
       <c r="E36">
-        <v>-2.917999999999999</v>
+        <v>-1.895000000000003</v>
       </c>
       <c r="F36">
-        <v>34.782</v>
+        <v>35.805</v>
       </c>
       <c r="G36">
         <v>5.72</v>
@@ -4227,28 +4227,28 @@
         <v>12.22</v>
       </c>
       <c r="M36">
-        <v>1.8886626</v>
+        <v>1.9442115</v>
       </c>
       <c r="N36">
-        <v>10.3313374</v>
+        <v>10.2757885</v>
       </c>
       <c r="O36">
-        <v>2.06626748</v>
+        <v>2.0551577</v>
       </c>
       <c r="P36">
-        <v>8.265069919999998</v>
+        <v>8.220630799999999</v>
       </c>
       <c r="Q36">
-        <v>13.64506992</v>
+        <v>13.6006308</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.105324598075571</v>
+        <v>0.1061106607771302</v>
       </c>
       <c r="T36">
-        <v>1.003670237877984</v>
+        <v>1.016924384300935</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.470186893095674</v>
+        <v>6.285324410435798</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08417592950513465</v>
+        <v>0.08406802428039242</v>
       </c>
       <c r="C37">
-        <v>77.39837411906254</v>
+        <v>76.67844745139323</v>
       </c>
       <c r="D37">
-        <v>107.4833741190625</v>
+        <v>107.7864474513932</v>
       </c>
       <c r="E37">
-        <v>-1.895000000000003</v>
+        <v>-0.8719999999999999</v>
       </c>
       <c r="F37">
-        <v>35.805</v>
+        <v>36.828</v>
       </c>
       <c r="G37">
         <v>5.72</v>
@@ -4309,28 +4309,28 @@
         <v>12.22</v>
       </c>
       <c r="M37">
-        <v>1.9442115</v>
+        <v>1.9997604</v>
       </c>
       <c r="N37">
-        <v>10.2757885</v>
+        <v>10.2202396</v>
       </c>
       <c r="O37">
-        <v>2.0551577</v>
+        <v>2.04404792</v>
       </c>
       <c r="P37">
-        <v>8.220630799999999</v>
+        <v>8.176191679999999</v>
       </c>
       <c r="Q37">
-        <v>13.6006308</v>
+        <v>13.55619168</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1061106607771302</v>
+        <v>0.1069212879381132</v>
       </c>
       <c r="T37">
-        <v>1.016924384300935</v>
+        <v>1.030592722799603</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.285324410435798</v>
+        <v>6.110732065701471</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08406802428039244</v>
+        <v>0.08425611905565021</v>
       </c>
       <c r="C38">
-        <v>76.6784474513932</v>
+        <v>75.12824740866748</v>
       </c>
       <c r="D38">
-        <v>107.7864474513932</v>
+        <v>107.2592474086675</v>
       </c>
       <c r="E38">
-        <v>-0.872000000000007</v>
+        <v>0.1509999999999962</v>
       </c>
       <c r="F38">
-        <v>36.828</v>
+        <v>37.851</v>
       </c>
       <c r="G38">
         <v>5.72</v>
@@ -4391,45 +4391,45 @@
         <v>12.22</v>
       </c>
       <c r="M38">
-        <v>1.9997604</v>
+        <v>2.0931603</v>
       </c>
       <c r="N38">
-        <v>10.2202396</v>
+        <v>10.1268397</v>
       </c>
       <c r="O38">
-        <v>2.04404792</v>
+        <v>2.02536794</v>
       </c>
       <c r="P38">
-        <v>8.176191679999999</v>
+        <v>8.101471759999999</v>
       </c>
       <c r="Q38">
-        <v>13.55619168</v>
+        <v>13.48147176</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1069212879381132</v>
+        <v>0.1077576492946829</v>
       </c>
       <c r="T38">
-        <v>1.030592722799603</v>
+        <v>1.044694976806166</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.110732065701471</v>
+        <v>5.838062187592607</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08425611905565021</v>
+        <v>0.08415621383090797</v>
       </c>
       <c r="C39">
-        <v>75.12824740866748</v>
+        <v>74.38462219954977</v>
       </c>
       <c r="D39">
-        <v>107.2592474086675</v>
+        <v>107.5386221995498</v>
       </c>
       <c r="E39">
-        <v>0.1509999999999962</v>
+        <v>1.173999999999999</v>
       </c>
       <c r="F39">
-        <v>37.851</v>
+        <v>38.874</v>
       </c>
       <c r="G39">
         <v>5.72</v>
@@ -4473,28 +4473,28 @@
         <v>12.22</v>
       </c>
       <c r="M39">
-        <v>2.0931603</v>
+        <v>2.1497322</v>
       </c>
       <c r="N39">
-        <v>10.1268397</v>
+        <v>10.0702678</v>
       </c>
       <c r="O39">
-        <v>2.02536794</v>
+        <v>2.01405356</v>
       </c>
       <c r="P39">
-        <v>8.101471759999999</v>
+        <v>8.056214239999999</v>
       </c>
       <c r="Q39">
-        <v>13.48147176</v>
+        <v>13.43621424</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1077576492946829</v>
+        <v>0.1086209900498516</v>
       </c>
       <c r="T39">
-        <v>1.044694976806166</v>
+        <v>1.059252142232295</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.838062187592607</v>
+        <v>5.684428972129643</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08415621383090797</v>
+        <v>0.08405630860616575</v>
       </c>
       <c r="C40">
-        <v>74.38462219954977</v>
+        <v>73.64245614853101</v>
       </c>
       <c r="D40">
-        <v>107.5386221995498</v>
+        <v>107.819456148531</v>
       </c>
       <c r="E40">
-        <v>1.173999999999999</v>
+        <v>2.196999999999996</v>
       </c>
       <c r="F40">
-        <v>38.874</v>
+        <v>39.897</v>
       </c>
       <c r="G40">
         <v>5.72</v>
@@ -4555,28 +4555,28 @@
         <v>12.22</v>
       </c>
       <c r="M40">
-        <v>2.1497322</v>
+        <v>2.2063041</v>
       </c>
       <c r="N40">
-        <v>10.0702678</v>
+        <v>10.0136959</v>
       </c>
       <c r="O40">
-        <v>2.01405356</v>
+        <v>2.00273918</v>
       </c>
       <c r="P40">
-        <v>8.056214239999999</v>
+        <v>8.010956719999999</v>
       </c>
       <c r="Q40">
-        <v>13.43621424</v>
+        <v>13.39095672</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1086209900498516</v>
+        <v>0.1095126370592881</v>
       </c>
       <c r="T40">
-        <v>1.059252142232295</v>
+        <v>1.074286591770757</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.684428972129643</v>
+        <v>5.538674383100679</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08405630860616575</v>
+        <v>0.08395640338142353</v>
       </c>
       <c r="C41">
-        <v>73.64245614853101</v>
+        <v>72.90176071718822</v>
       </c>
       <c r="D41">
-        <v>107.819456148531</v>
+        <v>108.1017607171882</v>
       </c>
       <c r="E41">
-        <v>2.196999999999996</v>
+        <v>3.219999999999999</v>
       </c>
       <c r="F41">
-        <v>39.897</v>
+        <v>40.92</v>
       </c>
       <c r="G41">
         <v>5.72</v>
@@ -4637,28 +4637,28 @@
         <v>12.22</v>
       </c>
       <c r="M41">
-        <v>2.2063041</v>
+        <v>2.262876</v>
       </c>
       <c r="N41">
-        <v>10.0136959</v>
+        <v>9.957123999999999</v>
       </c>
       <c r="O41">
-        <v>2.00273918</v>
+        <v>1.9914248</v>
       </c>
       <c r="P41">
-        <v>8.010956719999999</v>
+        <v>7.965699199999999</v>
       </c>
       <c r="Q41">
-        <v>13.39095672</v>
+        <v>13.3456992</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1095126370592881</v>
+        <v>0.1104340056357059</v>
       </c>
       <c r="T41">
-        <v>1.074286591770757</v>
+        <v>1.089822189627167</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.538674383100679</v>
+        <v>5.400207523523162</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08395640338142353</v>
+        <v>0.08385649815668131</v>
       </c>
       <c r="C42">
-        <v>72.90176071718822</v>
+        <v>72.16254748745322</v>
       </c>
       <c r="D42">
-        <v>108.1017607171882</v>
+        <v>108.3855474874532</v>
       </c>
       <c r="E42">
-        <v>3.219999999999999</v>
+        <v>4.243000000000002</v>
       </c>
       <c r="F42">
-        <v>40.92</v>
+        <v>41.943</v>
       </c>
       <c r="G42">
         <v>5.72</v>
@@ -4719,28 +4719,28 @@
         <v>12.22</v>
       </c>
       <c r="M42">
-        <v>2.262876</v>
+        <v>2.319447900000001</v>
       </c>
       <c r="N42">
-        <v>9.957123999999999</v>
+        <v>9.900552099999999</v>
       </c>
       <c r="O42">
-        <v>1.9914248</v>
+        <v>1.98011042</v>
       </c>
       <c r="P42">
-        <v>7.965699199999999</v>
+        <v>7.920441679999999</v>
       </c>
       <c r="Q42">
-        <v>13.3456992</v>
+        <v>13.30044168</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1104340056357059</v>
+        <v>0.1113866070452226</v>
       </c>
       <c r="T42">
-        <v>1.089822189627167</v>
+        <v>1.105884417919387</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.400207523523162</v>
+        <v>5.268495144900645</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08385649815668131</v>
+        <v>0.0837565929319391</v>
       </c>
       <c r="C43">
-        <v>72.16254748745322</v>
+        <v>71.42482816319662</v>
       </c>
       <c r="D43">
-        <v>108.3855474874532</v>
+        <v>108.6708281631966</v>
       </c>
       <c r="E43">
-        <v>4.243000000000002</v>
+        <v>5.265999999999998</v>
       </c>
       <c r="F43">
-        <v>41.943</v>
+        <v>42.966</v>
       </c>
       <c r="G43">
         <v>5.72</v>
@@ -4801,28 +4801,28 @@
         <v>12.22</v>
       </c>
       <c r="M43">
-        <v>2.319447900000001</v>
+        <v>2.3760198</v>
       </c>
       <c r="N43">
-        <v>9.900552099999999</v>
+        <v>9.843980199999999</v>
       </c>
       <c r="O43">
-        <v>1.98011042</v>
+        <v>1.96879604</v>
       </c>
       <c r="P43">
-        <v>7.920441679999999</v>
+        <v>7.875184159999999</v>
       </c>
       <c r="Q43">
-        <v>13.30044168</v>
+        <v>13.25518416</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1113866070452226</v>
+        <v>0.1123720567792053</v>
       </c>
       <c r="T43">
-        <v>1.105884417919387</v>
+        <v>1.122500516152719</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.268495144900645</v>
+        <v>5.143054784307773</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0837565929319391</v>
+        <v>0.08365668770719686</v>
       </c>
       <c r="C44">
-        <v>71.42482816319664</v>
+        <v>70.68861457183706</v>
       </c>
       <c r="D44">
-        <v>108.6708281631966</v>
+        <v>108.9576145718371</v>
       </c>
       <c r="E44">
-        <v>5.265999999999991</v>
+        <v>6.288999999999994</v>
       </c>
       <c r="F44">
-        <v>42.96599999999999</v>
+        <v>43.989</v>
       </c>
       <c r="G44">
         <v>5.72</v>
@@ -4883,28 +4883,28 @@
         <v>12.22</v>
       </c>
       <c r="M44">
-        <v>2.3760198</v>
+        <v>2.4325917</v>
       </c>
       <c r="N44">
-        <v>9.843980199999999</v>
+        <v>9.787408299999999</v>
       </c>
       <c r="O44">
-        <v>1.96879604</v>
+        <v>1.95748166</v>
       </c>
       <c r="P44">
-        <v>7.875184159999999</v>
+        <v>7.829926639999999</v>
       </c>
       <c r="Q44">
-        <v>13.25518416</v>
+        <v>13.20992664</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1123720567792053</v>
+        <v>0.1133920836968366</v>
       </c>
       <c r="T44">
-        <v>1.122500516152719</v>
+        <v>1.139699635376694</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.143054784307774</v>
+        <v>5.023448859091314</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08365668770719686</v>
+        <v>0.08355678248245463</v>
       </c>
       <c r="C45">
-        <v>70.68861457183706</v>
+        <v>69.95391866597528</v>
       </c>
       <c r="D45">
-        <v>108.9576145718371</v>
+        <v>109.2459186659753</v>
       </c>
       <c r="E45">
-        <v>6.288999999999994</v>
+        <v>7.311999999999998</v>
       </c>
       <c r="F45">
-        <v>43.989</v>
+        <v>45.012</v>
       </c>
       <c r="G45">
         <v>5.72</v>
@@ -4965,28 +4965,28 @@
         <v>12.22</v>
       </c>
       <c r="M45">
-        <v>2.4325917</v>
+        <v>2.4891636</v>
       </c>
       <c r="N45">
-        <v>9.787408299999999</v>
+        <v>9.730836399999999</v>
       </c>
       <c r="O45">
-        <v>1.95748166</v>
+        <v>1.94616728</v>
       </c>
       <c r="P45">
-        <v>7.829926639999999</v>
+        <v>7.784669119999999</v>
       </c>
       <c r="Q45">
-        <v>13.20992664</v>
+        <v>13.16466912</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1133920836968366</v>
+        <v>0.1144485401472404</v>
       </c>
       <c r="T45">
-        <v>1.139699635376694</v>
+        <v>1.157513008858668</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.023448859091314</v>
+        <v>4.909279566839238</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08355678248245463</v>
+        <v>0.08345687725771242</v>
       </c>
       <c r="C46">
-        <v>69.95391866597528</v>
+        <v>69.22075252505498</v>
       </c>
       <c r="D46">
-        <v>109.2459186659753</v>
+        <v>109.535752525055</v>
       </c>
       <c r="E46">
-        <v>7.311999999999998</v>
+        <v>8.334999999999994</v>
       </c>
       <c r="F46">
-        <v>45.012</v>
+        <v>46.035</v>
       </c>
       <c r="G46">
         <v>5.72</v>
@@ -5047,28 +5047,28 @@
         <v>12.22</v>
       </c>
       <c r="M46">
-        <v>2.4891636</v>
+        <v>2.5457355</v>
       </c>
       <c r="N46">
-        <v>9.730836399999999</v>
+        <v>9.6742645</v>
       </c>
       <c r="O46">
-        <v>1.94616728</v>
+        <v>1.9348529</v>
       </c>
       <c r="P46">
-        <v>7.784669119999999</v>
+        <v>7.7394116</v>
       </c>
       <c r="Q46">
-        <v>13.16466912</v>
+        <v>13.1194116</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1144485401472404</v>
+        <v>0.1155434131958407</v>
       </c>
       <c r="T46">
-        <v>1.157513008858668</v>
+        <v>1.17597414137635</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.909279566839238</v>
+        <v>4.800184465353922</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08345687725771242</v>
+        <v>0.0833569720329702</v>
       </c>
       <c r="C47">
-        <v>69.22075252505498</v>
+        <v>68.48912835705008</v>
       </c>
       <c r="D47">
-        <v>109.535752525055</v>
+        <v>109.8271283570501</v>
       </c>
       <c r="E47">
-        <v>8.334999999999994</v>
+        <v>9.357999999999997</v>
       </c>
       <c r="F47">
-        <v>46.035</v>
+        <v>47.058</v>
       </c>
       <c r="G47">
         <v>5.72</v>
@@ -5129,28 +5129,28 @@
         <v>12.22</v>
       </c>
       <c r="M47">
-        <v>2.5457355</v>
+        <v>2.6023074</v>
       </c>
       <c r="N47">
-        <v>9.6742645</v>
+        <v>9.617692599999998</v>
       </c>
       <c r="O47">
-        <v>1.9348529</v>
+        <v>1.92353852</v>
       </c>
       <c r="P47">
-        <v>7.7394116</v>
+        <v>7.694154079999999</v>
       </c>
       <c r="Q47">
-        <v>13.1194116</v>
+        <v>13.07415408</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1155434131958407</v>
+        <v>0.1166788370980929</v>
       </c>
       <c r="T47">
-        <v>1.17597414137635</v>
+        <v>1.195119019542835</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.800184465353922</v>
+        <v>4.695832629150575</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0833569720329702</v>
+        <v>0.08325706680822796</v>
       </c>
       <c r="C48">
-        <v>68.48912835705008</v>
+        <v>67.7590585001785</v>
       </c>
       <c r="D48">
-        <v>109.8271283570501</v>
+        <v>110.1200585001785</v>
       </c>
       <c r="E48">
-        <v>9.357999999999997</v>
+        <v>10.381</v>
       </c>
       <c r="F48">
-        <v>47.058</v>
+        <v>48.081</v>
       </c>
       <c r="G48">
         <v>5.72</v>
@@ -5211,28 +5211,28 @@
         <v>12.22</v>
       </c>
       <c r="M48">
-        <v>2.6023074</v>
+        <v>2.6588793</v>
       </c>
       <c r="N48">
-        <v>9.617692599999998</v>
+        <v>9.561120699999998</v>
       </c>
       <c r="O48">
-        <v>1.92353852</v>
+        <v>1.91222414</v>
       </c>
       <c r="P48">
-        <v>7.694154079999999</v>
+        <v>7.648896559999999</v>
       </c>
       <c r="Q48">
-        <v>13.07415408</v>
+        <v>13.02889656</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1166788370980929</v>
+        <v>0.1178571071853358</v>
       </c>
       <c r="T48">
-        <v>1.195119019542835</v>
+        <v>1.214986345942018</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.695832629150575</v>
+        <v>4.595921296615456</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08325706680822796</v>
+        <v>0.08315716158348574</v>
       </c>
       <c r="C49">
-        <v>67.7590585001785</v>
+        <v>67.03055542464375</v>
       </c>
       <c r="D49">
-        <v>110.1200585001785</v>
+        <v>110.4145554246438</v>
       </c>
       <c r="E49">
-        <v>10.381</v>
+        <v>11.404</v>
       </c>
       <c r="F49">
-        <v>48.081</v>
+        <v>49.104</v>
       </c>
       <c r="G49">
         <v>5.72</v>
@@ -5293,28 +5293,28 @@
         <v>12.22</v>
       </c>
       <c r="M49">
-        <v>2.6588793</v>
+        <v>2.7154512</v>
       </c>
       <c r="N49">
-        <v>9.561120699999998</v>
+        <v>9.504548799999998</v>
       </c>
       <c r="O49">
-        <v>1.91222414</v>
+        <v>1.90090976</v>
       </c>
       <c r="P49">
-        <v>7.648896559999999</v>
+        <v>7.603639039999999</v>
       </c>
       <c r="Q49">
-        <v>13.02889656</v>
+        <v>12.98363904</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1178571071853358</v>
+        <v>0.1190806953528572</v>
       </c>
       <c r="T49">
-        <v>1.214986345942018</v>
+        <v>1.235617800279631</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.595921296615456</v>
+        <v>4.500172936269301</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08315716158348573</v>
+        <v>0.08403725635874351</v>
       </c>
       <c r="C50">
-        <v>67.03055542464379</v>
+        <v>63.46617869954777</v>
       </c>
       <c r="D50">
-        <v>110.4145554246438</v>
+        <v>107.8731786995478</v>
       </c>
       <c r="E50">
-        <v>11.404</v>
+        <v>12.42699999999999</v>
       </c>
       <c r="F50">
-        <v>49.104</v>
+        <v>50.127</v>
       </c>
       <c r="G50">
         <v>5.72</v>
@@ -5375,45 +5375,45 @@
         <v>12.22</v>
       </c>
       <c r="M50">
-        <v>2.7154512</v>
+        <v>2.8973406</v>
       </c>
       <c r="N50">
-        <v>9.504548799999998</v>
+        <v>9.322659399999999</v>
       </c>
       <c r="O50">
-        <v>1.90090976</v>
+        <v>1.86453188</v>
       </c>
       <c r="P50">
-        <v>7.603639039999999</v>
+        <v>7.45812752</v>
       </c>
       <c r="Q50">
-        <v>12.98363904</v>
+        <v>12.83812752</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1190806953528572</v>
+        <v>0.1203522673700853</v>
       </c>
       <c r="T50">
-        <v>1.235617800279631</v>
+        <v>1.257058331257934</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.500172936269301</v>
+        <v>4.217660843878694</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08403725635874351</v>
+        <v>0.08395735113400128</v>
       </c>
       <c r="C51">
-        <v>63.46617869954777</v>
+        <v>62.66907568483314</v>
       </c>
       <c r="D51">
-        <v>107.8731786995478</v>
+        <v>108.0990756848331</v>
       </c>
       <c r="E51">
-        <v>12.42699999999999</v>
+        <v>13.45</v>
       </c>
       <c r="F51">
-        <v>50.127</v>
+        <v>51.15</v>
       </c>
       <c r="G51">
         <v>5.72</v>
@@ -5457,28 +5457,28 @@
         <v>12.22</v>
       </c>
       <c r="M51">
-        <v>2.8973406</v>
+        <v>2.95647</v>
       </c>
       <c r="N51">
-        <v>9.322659399999999</v>
+        <v>9.263529999999999</v>
       </c>
       <c r="O51">
-        <v>1.86453188</v>
+        <v>1.852706</v>
       </c>
       <c r="P51">
-        <v>7.45812752</v>
+        <v>7.410824</v>
       </c>
       <c r="Q51">
-        <v>12.83812752</v>
+        <v>12.790824</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1203522673700853</v>
+        <v>0.1216747022680026</v>
       </c>
       <c r="T51">
-        <v>1.257058331257934</v>
+        <v>1.27935648347537</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.217660843878694</v>
+        <v>4.13330762700112</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08395735113400128</v>
+        <v>0.08387744590925908</v>
       </c>
       <c r="C52">
-        <v>62.66907568483314</v>
+        <v>61.87292075625955</v>
       </c>
       <c r="D52">
-        <v>108.0990756848331</v>
+        <v>108.3259207562595</v>
       </c>
       <c r="E52">
-        <v>13.45</v>
+        <v>14.473</v>
       </c>
       <c r="F52">
-        <v>51.15</v>
+        <v>52.173</v>
       </c>
       <c r="G52">
         <v>5.72</v>
@@ -5539,28 +5539,28 @@
         <v>12.22</v>
       </c>
       <c r="M52">
-        <v>2.95647</v>
+        <v>3.0155994</v>
       </c>
       <c r="N52">
-        <v>9.263529999999999</v>
+        <v>9.2044006</v>
       </c>
       <c r="O52">
-        <v>1.852706</v>
+        <v>1.84088012</v>
       </c>
       <c r="P52">
-        <v>7.410824</v>
+        <v>7.36352048</v>
       </c>
       <c r="Q52">
-        <v>12.790824</v>
+        <v>12.74352048</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1216747022680026</v>
+        <v>0.1230511141005287</v>
       </c>
       <c r="T52">
-        <v>1.27935648347537</v>
+        <v>1.302564764354742</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.13330762700112</v>
+        <v>4.052262379412862</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08387744590925908</v>
+        <v>0.08525354068451683</v>
       </c>
       <c r="C53">
-        <v>61.87292075625955</v>
+        <v>57.07163543658039</v>
       </c>
       <c r="D53">
-        <v>108.3259207562595</v>
+        <v>104.5476354365804</v>
       </c>
       <c r="E53">
-        <v>14.473</v>
+        <v>15.496</v>
       </c>
       <c r="F53">
-        <v>52.173</v>
+        <v>53.196</v>
       </c>
       <c r="G53">
         <v>5.72</v>
@@ -5621,45 +5621,45 @@
         <v>12.22</v>
       </c>
       <c r="M53">
-        <v>3.0155994</v>
+        <v>3.2609148</v>
       </c>
       <c r="N53">
-        <v>9.2044006</v>
+        <v>8.959085199999999</v>
       </c>
       <c r="O53">
-        <v>1.84088012</v>
+        <v>1.79181704</v>
       </c>
       <c r="P53">
-        <v>7.36352048</v>
+        <v>7.167268159999999</v>
       </c>
       <c r="Q53">
-        <v>12.74352048</v>
+        <v>12.54726816</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1230511141005287</v>
+        <v>0.1244848764260768</v>
       </c>
       <c r="T53">
-        <v>1.302564764354742</v>
+        <v>1.32674005693742</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.052262379412862</v>
+        <v>3.74741468253019</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08525354068451683</v>
+        <v>0.08520163545977462</v>
       </c>
       <c r="C54">
-        <v>57.07163543658039</v>
+        <v>56.18635988507803</v>
       </c>
       <c r="D54">
-        <v>104.5476354365804</v>
+        <v>104.685359885078</v>
       </c>
       <c r="E54">
-        <v>15.496</v>
+        <v>16.519</v>
       </c>
       <c r="F54">
-        <v>53.196</v>
+        <v>54.219</v>
       </c>
       <c r="G54">
         <v>5.72</v>
@@ -5703,28 +5703,28 @@
         <v>12.22</v>
       </c>
       <c r="M54">
-        <v>3.2609148</v>
+        <v>3.3236247</v>
       </c>
       <c r="N54">
-        <v>8.959085199999999</v>
+        <v>8.896375299999999</v>
       </c>
       <c r="O54">
-        <v>1.79181704</v>
+        <v>1.77927506</v>
       </c>
       <c r="P54">
-        <v>7.167268159999999</v>
+        <v>7.117100239999999</v>
       </c>
       <c r="Q54">
-        <v>12.54726816</v>
+        <v>12.49710024</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1244848764260768</v>
+        <v>0.1259796499144141</v>
       </c>
       <c r="T54">
-        <v>1.32674005693742</v>
+        <v>1.351944085374681</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.74741468253019</v>
+        <v>3.67670874512396</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08520163545977462</v>
+        <v>0.08514973023503239</v>
       </c>
       <c r="C55">
-        <v>56.18635988507803</v>
+        <v>55.30144767118486</v>
       </c>
       <c r="D55">
-        <v>104.685359885078</v>
+        <v>104.8234476711849</v>
       </c>
       <c r="E55">
-        <v>16.519</v>
+        <v>17.542</v>
       </c>
       <c r="F55">
-        <v>54.219</v>
+        <v>55.242</v>
       </c>
       <c r="G55">
         <v>5.72</v>
@@ -5785,28 +5785,28 @@
         <v>12.22</v>
       </c>
       <c r="M55">
-        <v>3.3236247</v>
+        <v>3.3863346</v>
       </c>
       <c r="N55">
-        <v>8.896375299999999</v>
+        <v>8.833665399999999</v>
       </c>
       <c r="O55">
-        <v>1.77927506</v>
+        <v>1.76673308</v>
       </c>
       <c r="P55">
-        <v>7.117100239999999</v>
+        <v>7.066932319999999</v>
       </c>
       <c r="Q55">
-        <v>12.49710024</v>
+        <v>12.44693232</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1259796499144141</v>
+        <v>0.1275394135544182</v>
       </c>
       <c r="T55">
-        <v>1.351944085374681</v>
+        <v>1.378243941135302</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.67670874512396</v>
+        <v>3.608621546140183</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08514973023503239</v>
+        <v>0.08509782501029016</v>
       </c>
       <c r="C56">
-        <v>55.30144767118486</v>
+        <v>54.41690023460798</v>
       </c>
       <c r="D56">
-        <v>104.8234476711849</v>
+        <v>104.961900234608</v>
       </c>
       <c r="E56">
-        <v>17.542</v>
+        <v>18.565</v>
       </c>
       <c r="F56">
-        <v>55.242</v>
+        <v>56.265</v>
       </c>
       <c r="G56">
         <v>5.72</v>
@@ -5867,28 +5867,28 @@
         <v>12.22</v>
       </c>
       <c r="M56">
-        <v>3.3863346</v>
+        <v>3.4490445</v>
       </c>
       <c r="N56">
-        <v>8.833665399999999</v>
+        <v>8.770955499999999</v>
       </c>
       <c r="O56">
-        <v>1.76673308</v>
+        <v>1.7541911</v>
       </c>
       <c r="P56">
-        <v>7.066932319999999</v>
+        <v>7.0167644</v>
       </c>
       <c r="Q56">
-        <v>12.44693232</v>
+        <v>12.3967644</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1275394135544182</v>
+        <v>0.129168500022867</v>
       </c>
       <c r="T56">
-        <v>1.378243941135302</v>
+        <v>1.405712679374172</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.608621546140183</v>
+        <v>3.543010245301271</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08509782501029016</v>
+        <v>0.08630031978554795</v>
       </c>
       <c r="C57">
-        <v>54.41690023460798</v>
+        <v>50.27747702359215</v>
       </c>
       <c r="D57">
-        <v>104.961900234608</v>
+        <v>101.8454770235922</v>
       </c>
       <c r="E57">
-        <v>18.565</v>
+        <v>19.588</v>
       </c>
       <c r="F57">
-        <v>56.265</v>
+        <v>57.288</v>
       </c>
       <c r="G57">
         <v>5.72</v>
@@ -5949,45 +5949,45 @@
         <v>12.22</v>
       </c>
       <c r="M57">
-        <v>3.4490445</v>
+        <v>3.6721608</v>
       </c>
       <c r="N57">
-        <v>8.770955499999999</v>
+        <v>8.547839199999999</v>
       </c>
       <c r="O57">
-        <v>1.7541911</v>
+        <v>1.70956784</v>
       </c>
       <c r="P57">
-        <v>7.0167644</v>
+        <v>6.838271359999998</v>
       </c>
       <c r="Q57">
-        <v>12.3967644</v>
+        <v>12.21827136</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.129168500022867</v>
+        <v>0.1308716358762453</v>
       </c>
       <c r="T57">
-        <v>1.405712679374172</v>
+        <v>1.434429996623899</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.543010245301271</v>
+        <v>3.327740985634398</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08630031978554795</v>
+        <v>0.08627081456080571</v>
       </c>
       <c r="C58">
-        <v>50.27747702359215</v>
+        <v>49.32872741170939</v>
       </c>
       <c r="D58">
-        <v>101.8454770235922</v>
+        <v>101.9197274117094</v>
       </c>
       <c r="E58">
-        <v>19.588</v>
+        <v>20.611</v>
       </c>
       <c r="F58">
-        <v>57.288</v>
+        <v>58.31100000000001</v>
       </c>
       <c r="G58">
         <v>5.72</v>
@@ -6031,28 +6031,28 @@
         <v>12.22</v>
       </c>
       <c r="M58">
-        <v>3.6721608</v>
+        <v>3.737735100000001</v>
       </c>
       <c r="N58">
-        <v>8.547839199999999</v>
+        <v>8.482264899999999</v>
       </c>
       <c r="O58">
-        <v>1.70956784</v>
+        <v>1.69645298</v>
       </c>
       <c r="P58">
-        <v>6.838271359999998</v>
+        <v>6.785811919999999</v>
       </c>
       <c r="Q58">
-        <v>12.21827136</v>
+        <v>12.16581192</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1308716358762453</v>
+        <v>0.132653987350711</v>
       </c>
       <c r="T58">
-        <v>1.434429996623899</v>
+        <v>1.464483003048033</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.327740985634398</v>
+        <v>3.269359564833794</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08627081456080571</v>
+        <v>0.08624130933606348</v>
       </c>
       <c r="C59">
-        <v>49.32872741170939</v>
+        <v>48.38008614322227</v>
       </c>
       <c r="D59">
-        <v>101.9197274117094</v>
+        <v>101.9940861432223</v>
       </c>
       <c r="E59">
-        <v>20.611</v>
+        <v>21.634</v>
       </c>
       <c r="F59">
-        <v>58.31100000000001</v>
+        <v>59.334</v>
       </c>
       <c r="G59">
         <v>5.72</v>
@@ -6113,28 +6113,28 @@
         <v>12.22</v>
       </c>
       <c r="M59">
-        <v>3.737735100000001</v>
+        <v>3.8033094</v>
       </c>
       <c r="N59">
-        <v>8.482264899999999</v>
+        <v>8.416690599999999</v>
       </c>
       <c r="O59">
-        <v>1.69645298</v>
+        <v>1.68333812</v>
       </c>
       <c r="P59">
-        <v>6.785811919999999</v>
+        <v>6.733352479999999</v>
       </c>
       <c r="Q59">
-        <v>12.16581192</v>
+        <v>12.11335248</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.132653987350711</v>
+        <v>0.1345212127049131</v>
       </c>
       <c r="T59">
-        <v>1.464483003048033</v>
+        <v>1.495967105016173</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.269359564833794</v>
+        <v>3.212991296474591</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08624130933606348</v>
+        <v>0.08621180411132127</v>
       </c>
       <c r="C60">
-        <v>48.38008614322228</v>
+        <v>47.43155345543983</v>
       </c>
       <c r="D60">
-        <v>101.9940861432223</v>
+        <v>102.0685534554398</v>
       </c>
       <c r="E60">
-        <v>21.63399999999999</v>
+        <v>22.65699999999999</v>
       </c>
       <c r="F60">
-        <v>59.334</v>
+        <v>60.35699999999999</v>
       </c>
       <c r="G60">
         <v>5.72</v>
@@ -6195,28 +6195,28 @@
         <v>12.22</v>
       </c>
       <c r="M60">
-        <v>3.8033094</v>
+        <v>3.8688837</v>
       </c>
       <c r="N60">
-        <v>8.416690599999999</v>
+        <v>8.351116299999999</v>
       </c>
       <c r="O60">
-        <v>1.68333812</v>
+        <v>1.67022326</v>
       </c>
       <c r="P60">
-        <v>6.733352479999999</v>
+        <v>6.680893039999999</v>
       </c>
       <c r="Q60">
-        <v>12.11335248</v>
+        <v>12.06089304</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.134521212704913</v>
+        <v>0.1364795222227348</v>
       </c>
       <c r="T60">
-        <v>1.495967105016173</v>
+        <v>1.528987016836417</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.212991296474591</v>
+        <v>3.158533816873327</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08621180411132127</v>
+        <v>0.08618229888657905</v>
       </c>
       <c r="C61">
-        <v>47.43155345543983</v>
+        <v>46.4831295863648</v>
       </c>
       <c r="D61">
-        <v>102.0685534554398</v>
+        <v>102.1431295863648</v>
       </c>
       <c r="E61">
-        <v>22.65699999999999</v>
+        <v>23.67999999999999</v>
       </c>
       <c r="F61">
-        <v>60.35699999999999</v>
+        <v>61.38</v>
       </c>
       <c r="G61">
         <v>5.72</v>
@@ -6277,28 +6277,28 @@
         <v>12.22</v>
       </c>
       <c r="M61">
-        <v>3.8688837</v>
+        <v>3.934458</v>
       </c>
       <c r="N61">
-        <v>8.351116299999999</v>
+        <v>8.285542</v>
       </c>
       <c r="O61">
-        <v>1.67022326</v>
+        <v>1.6571084</v>
       </c>
       <c r="P61">
-        <v>6.680893039999999</v>
+        <v>6.628433599999999</v>
       </c>
       <c r="Q61">
-        <v>12.06089304</v>
+        <v>12.0084336</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1364795222227348</v>
+        <v>0.1385357472164476</v>
       </c>
       <c r="T61">
-        <v>1.528987016836417</v>
+        <v>1.563657924247674</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.158533816873327</v>
+        <v>3.105891586592105</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08618229888657905</v>
+        <v>0.08615279366183681</v>
       </c>
       <c r="C62">
-        <v>46.4831295863648</v>
+        <v>45.53481477469591</v>
       </c>
       <c r="D62">
-        <v>102.1431295863648</v>
+        <v>102.2178147746959</v>
       </c>
       <c r="E62">
-        <v>23.67999999999999</v>
+        <v>24.703</v>
       </c>
       <c r="F62">
-        <v>61.38</v>
+        <v>62.403</v>
       </c>
       <c r="G62">
         <v>5.72</v>
@@ -6359,28 +6359,28 @@
         <v>12.22</v>
       </c>
       <c r="M62">
-        <v>3.934458</v>
+        <v>4.0000323</v>
       </c>
       <c r="N62">
-        <v>8.285542</v>
+        <v>8.219967699999998</v>
       </c>
       <c r="O62">
-        <v>1.6571084</v>
+        <v>1.64399354</v>
       </c>
       <c r="P62">
-        <v>6.628433599999999</v>
+        <v>6.575974159999999</v>
       </c>
       <c r="Q62">
-        <v>12.0084336</v>
+        <v>11.95597416</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1385357472164476</v>
+        <v>0.1406974196457354</v>
       </c>
       <c r="T62">
-        <v>1.563657924247674</v>
+        <v>1.60010682691079</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.105891586592105</v>
+        <v>3.054975331074201</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08615279366183681</v>
+        <v>0.08612328843709458</v>
       </c>
       <c r="C63">
-        <v>45.53481477469591</v>
+        <v>44.58660925983055</v>
       </c>
       <c r="D63">
-        <v>102.2178147746959</v>
+        <v>102.2926092598305</v>
       </c>
       <c r="E63">
-        <v>24.703</v>
+        <v>25.72599999999999</v>
       </c>
       <c r="F63">
-        <v>62.403</v>
+        <v>63.42599999999999</v>
       </c>
       <c r="G63">
         <v>5.72</v>
@@ -6441,28 +6441,28 @@
         <v>12.22</v>
       </c>
       <c r="M63">
-        <v>4.0000323</v>
+        <v>4.0656066</v>
       </c>
       <c r="N63">
-        <v>8.219967699999998</v>
+        <v>8.1543934</v>
       </c>
       <c r="O63">
-        <v>1.64399354</v>
+        <v>1.63087868</v>
       </c>
       <c r="P63">
-        <v>6.575974159999999</v>
+        <v>6.52351472</v>
       </c>
       <c r="Q63">
-        <v>11.95597416</v>
+        <v>11.90351472</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1406974196457354</v>
+        <v>0.1429728643081436</v>
       </c>
       <c r="T63">
-        <v>1.60010682691079</v>
+        <v>1.638474092871965</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.054975331074201</v>
+        <v>3.005701535411715</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08612328843709458</v>
+        <v>0.09002498321235236</v>
       </c>
       <c r="C64">
-        <v>44.58660925983055</v>
+        <v>34.53896956284832</v>
       </c>
       <c r="D64">
-        <v>102.2926092598305</v>
+        <v>93.26796956284832</v>
       </c>
       <c r="E64">
-        <v>25.72599999999999</v>
+        <v>26.749</v>
       </c>
       <c r="F64">
-        <v>63.42599999999999</v>
+        <v>64.449</v>
       </c>
       <c r="G64">
         <v>5.72</v>
@@ -6523,45 +6523,45 @@
         <v>12.22</v>
       </c>
       <c r="M64">
-        <v>4.0656066</v>
+        <v>4.6338831</v>
       </c>
       <c r="N64">
-        <v>8.1543934</v>
+        <v>7.586116899999999</v>
       </c>
       <c r="O64">
-        <v>1.63087868</v>
+        <v>1.51722338</v>
       </c>
       <c r="P64">
-        <v>6.52351472</v>
+        <v>6.068893519999999</v>
       </c>
       <c r="Q64">
-        <v>11.90351472</v>
+        <v>11.44889352</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1429728643081436</v>
+        <v>0.1453713059793307</v>
       </c>
       <c r="T64">
-        <v>1.638474092871965</v>
+        <v>1.678915265101311</v>
       </c>
       <c r="U64">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.005701535411715</v>
+        <v>2.637097168031709</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09002498321235236</v>
+        <v>0.09005787798761014</v>
       </c>
       <c r="C65">
-        <v>34.53896956284832</v>
+        <v>33.44664791804696</v>
       </c>
       <c r="D65">
-        <v>93.26796956284832</v>
+        <v>93.19864791804696</v>
       </c>
       <c r="E65">
-        <v>26.749</v>
+        <v>27.77199999999999</v>
       </c>
       <c r="F65">
-        <v>64.449</v>
+        <v>65.47199999999999</v>
       </c>
       <c r="G65">
         <v>5.72</v>
@@ -6605,28 +6605,28 @@
         <v>12.22</v>
       </c>
       <c r="M65">
-        <v>4.6338831</v>
+        <v>4.7074368</v>
       </c>
       <c r="N65">
-        <v>7.586116899999999</v>
+        <v>7.512563199999999</v>
       </c>
       <c r="O65">
-        <v>1.51722338</v>
+        <v>1.50251264</v>
       </c>
       <c r="P65">
-        <v>6.068893519999999</v>
+        <v>6.010050559999999</v>
       </c>
       <c r="Q65">
-        <v>11.44889352</v>
+        <v>11.39005056</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1453713059793307</v>
+        <v>0.1479029944100282</v>
       </c>
       <c r="T65">
-        <v>1.678915265101311</v>
+        <v>1.721603169121177</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.637097168031709</v>
+        <v>2.595892524781214</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09005787798761014</v>
+        <v>0.09009077276286791</v>
       </c>
       <c r="C66">
-        <v>33.44664791804696</v>
+        <v>32.35442924367418</v>
       </c>
       <c r="D66">
-        <v>93.19864791804696</v>
+        <v>93.12942924367418</v>
       </c>
       <c r="E66">
-        <v>27.77199999999999</v>
+        <v>28.795</v>
       </c>
       <c r="F66">
-        <v>65.47199999999999</v>
+        <v>66.495</v>
       </c>
       <c r="G66">
         <v>5.72</v>
@@ -6687,28 +6687,28 @@
         <v>12.22</v>
       </c>
       <c r="M66">
-        <v>4.7074368</v>
+        <v>4.780990500000001</v>
       </c>
       <c r="N66">
-        <v>7.512563199999999</v>
+        <v>7.439009499999998</v>
       </c>
       <c r="O66">
-        <v>1.50251264</v>
+        <v>1.4878019</v>
       </c>
       <c r="P66">
-        <v>6.010050559999999</v>
+        <v>5.951207599999998</v>
       </c>
       <c r="Q66">
-        <v>11.39005056</v>
+        <v>11.3312076</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1479029944100282</v>
+        <v>0.1505793507510512</v>
       </c>
       <c r="T66">
-        <v>1.721603169121177</v>
+        <v>1.766730381942177</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.595892524781214</v>
+        <v>2.555955716707657</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09009077276286791</v>
+        <v>0.09012366753812569</v>
       </c>
       <c r="C67">
-        <v>32.35442924367418</v>
+        <v>31.26231331047165</v>
       </c>
       <c r="D67">
-        <v>93.12942924367418</v>
+        <v>93.06031331047166</v>
       </c>
       <c r="E67">
-        <v>28.795</v>
+        <v>29.818</v>
       </c>
       <c r="F67">
-        <v>66.495</v>
+        <v>67.518</v>
       </c>
       <c r="G67">
         <v>5.72</v>
@@ -6769,28 +6769,28 @@
         <v>12.22</v>
       </c>
       <c r="M67">
-        <v>4.780990500000001</v>
+        <v>4.8545442</v>
       </c>
       <c r="N67">
-        <v>7.439009499999998</v>
+        <v>7.365455799999999</v>
       </c>
       <c r="O67">
-        <v>1.4878019</v>
+        <v>1.47309116</v>
       </c>
       <c r="P67">
-        <v>5.951207599999998</v>
+        <v>5.892364639999998</v>
       </c>
       <c r="Q67">
-        <v>11.3312076</v>
+        <v>11.27236464</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1505793507510512</v>
+        <v>0.1534131398180167</v>
       </c>
       <c r="T67">
-        <v>1.766730381942177</v>
+        <v>1.814512136693825</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.555955716707657</v>
+        <v>2.517229114939359</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09012366753812569</v>
+        <v>0.09224696231338346</v>
       </c>
       <c r="C68">
-        <v>31.26231331047165</v>
+        <v>25.98511740196894</v>
       </c>
       <c r="D68">
-        <v>93.06031331047166</v>
+        <v>88.80611740196893</v>
       </c>
       <c r="E68">
-        <v>29.818</v>
+        <v>30.84099999999999</v>
       </c>
       <c r="F68">
-        <v>67.518</v>
+        <v>68.541</v>
       </c>
       <c r="G68">
         <v>5.72</v>
@@ -6851,45 +6851,45 @@
         <v>12.22</v>
       </c>
       <c r="M68">
-        <v>4.8545442</v>
+        <v>5.1954078</v>
       </c>
       <c r="N68">
-        <v>7.365455799999999</v>
+        <v>7.024592199999999</v>
       </c>
       <c r="O68">
-        <v>1.47309116</v>
+        <v>1.40491844</v>
       </c>
       <c r="P68">
-        <v>5.892364639999998</v>
+        <v>5.61967376</v>
       </c>
       <c r="Q68">
-        <v>11.27236464</v>
+        <v>10.99967376</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1534131398180167</v>
+        <v>0.1564186736769196</v>
       </c>
       <c r="T68">
-        <v>1.814512136693825</v>
+        <v>1.865189755369815</v>
       </c>
       <c r="U68">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.517229114939359</v>
+        <v>2.352077155521844</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09224696231338346</v>
+        <v>0.09231105708864124</v>
       </c>
       <c r="C69">
-        <v>25.98511740196894</v>
+        <v>24.83973772512033</v>
       </c>
       <c r="D69">
-        <v>88.80611740196893</v>
+        <v>88.68373772512034</v>
       </c>
       <c r="E69">
-        <v>30.84099999999999</v>
+        <v>31.864</v>
       </c>
       <c r="F69">
-        <v>68.541</v>
+        <v>69.56400000000001</v>
       </c>
       <c r="G69">
         <v>5.72</v>
@@ -6933,28 +6933,28 @@
         <v>12.22</v>
       </c>
       <c r="M69">
-        <v>5.1954078</v>
+        <v>5.272951200000001</v>
       </c>
       <c r="N69">
-        <v>7.024592199999999</v>
+        <v>6.947048799999997</v>
       </c>
       <c r="O69">
-        <v>1.40491844</v>
+        <v>1.389409759999999</v>
       </c>
       <c r="P69">
-        <v>5.61967376</v>
+        <v>5.557639039999998</v>
       </c>
       <c r="Q69">
-        <v>10.99967376</v>
+        <v>10.93763904</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1564186736769196</v>
+        <v>0.1596120534020039</v>
       </c>
       <c r="T69">
-        <v>1.865189755369815</v>
+        <v>1.919034725213054</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.352077155521844</v>
+        <v>2.317487785587698</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09231105708864124</v>
+        <v>0.09237515186389901</v>
       </c>
       <c r="C70">
-        <v>24.83973772512033</v>
+        <v>23.69469487585339</v>
       </c>
       <c r="D70">
-        <v>88.68373772512034</v>
+        <v>88.56169487585339</v>
       </c>
       <c r="E70">
-        <v>31.864</v>
+        <v>32.887</v>
       </c>
       <c r="F70">
-        <v>69.56400000000001</v>
+        <v>70.587</v>
       </c>
       <c r="G70">
         <v>5.72</v>
@@ -7015,28 +7015,28 @@
         <v>12.22</v>
       </c>
       <c r="M70">
-        <v>5.272951200000001</v>
+        <v>5.350494600000001</v>
       </c>
       <c r="N70">
-        <v>6.947048799999997</v>
+        <v>6.869505399999998</v>
       </c>
       <c r="O70">
-        <v>1.389409759999999</v>
+        <v>1.37390108</v>
       </c>
       <c r="P70">
-        <v>5.557639039999998</v>
+        <v>5.495604319999998</v>
       </c>
       <c r="Q70">
-        <v>10.93763904</v>
+        <v>10.87560432</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1596120534020039</v>
+        <v>0.1630114576254807</v>
       </c>
       <c r="T70">
-        <v>1.919034725213054</v>
+        <v>1.976353564078439</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.317487785587698</v>
+        <v>2.283901006086428</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09237515186389901</v>
+        <v>0.09243924663915679</v>
       </c>
       <c r="C71">
-        <v>23.69469487585339</v>
+        <v>22.54998746549504</v>
       </c>
       <c r="D71">
-        <v>88.56169487585339</v>
+        <v>88.43998746549504</v>
       </c>
       <c r="E71">
-        <v>32.887</v>
+        <v>33.91</v>
       </c>
       <c r="F71">
-        <v>70.587</v>
+        <v>71.61</v>
       </c>
       <c r="G71">
         <v>5.72</v>
@@ -7097,28 +7097,28 @@
         <v>12.22</v>
       </c>
       <c r="M71">
-        <v>5.350494600000001</v>
+        <v>5.428038000000001</v>
       </c>
       <c r="N71">
-        <v>6.869505399999998</v>
+        <v>6.791961999999998</v>
       </c>
       <c r="O71">
-        <v>1.37390108</v>
+        <v>1.3583924</v>
       </c>
       <c r="P71">
-        <v>5.495604319999998</v>
+        <v>5.433569599999998</v>
       </c>
       <c r="Q71">
-        <v>10.87560432</v>
+        <v>10.8135696</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1630114576254807</v>
+        <v>0.1666374887971893</v>
       </c>
       <c r="T71">
-        <v>1.976353564078439</v>
+        <v>2.037493658868181</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.283901006086428</v>
+        <v>2.251273848856621</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09243924663915679</v>
+        <v>0.09250334141441457</v>
       </c>
       <c r="C72">
-        <v>22.54998746549504</v>
+        <v>21.40561411299541</v>
       </c>
       <c r="D72">
-        <v>88.43998746549504</v>
+        <v>88.31861411299542</v>
       </c>
       <c r="E72">
-        <v>33.91</v>
+        <v>34.93300000000001</v>
       </c>
       <c r="F72">
-        <v>71.61</v>
+        <v>72.63300000000001</v>
       </c>
       <c r="G72">
         <v>5.72</v>
@@ -7179,28 +7179,28 @@
         <v>12.22</v>
       </c>
       <c r="M72">
-        <v>5.428038000000001</v>
+        <v>5.505581400000001</v>
       </c>
       <c r="N72">
-        <v>6.791961999999998</v>
+        <v>6.714418599999997</v>
       </c>
       <c r="O72">
-        <v>1.3583924</v>
+        <v>1.34288372</v>
       </c>
       <c r="P72">
-        <v>5.433569599999998</v>
+        <v>5.371534879999998</v>
       </c>
       <c r="Q72">
-        <v>10.8135696</v>
+        <v>10.75153488</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1666374887971893</v>
+        <v>0.1705135910841882</v>
       </c>
       <c r="T72">
-        <v>2.037493658868181</v>
+        <v>2.102850311919287</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.251273848856621</v>
+        <v>2.219565766478359</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09250334141441456</v>
+        <v>0.09256743618967234</v>
       </c>
       <c r="C73">
-        <v>21.40561411299544</v>
+        <v>20.26157344487558</v>
       </c>
       <c r="D73">
-        <v>88.31861411299543</v>
+        <v>88.19757344487557</v>
       </c>
       <c r="E73">
-        <v>34.93299999999999</v>
+        <v>35.95599999999999</v>
       </c>
       <c r="F73">
-        <v>72.633</v>
+        <v>73.65599999999999</v>
       </c>
       <c r="G73">
         <v>5.72</v>
@@ -7261,28 +7261,28 @@
         <v>12.22</v>
       </c>
       <c r="M73">
-        <v>5.505581400000001</v>
+        <v>5.5831248</v>
       </c>
       <c r="N73">
-        <v>6.714418599999998</v>
+        <v>6.636875199999999</v>
       </c>
       <c r="O73">
-        <v>1.34288372</v>
+        <v>1.32737504</v>
       </c>
       <c r="P73">
-        <v>5.371534879999999</v>
+        <v>5.309500159999999</v>
       </c>
       <c r="Q73">
-        <v>10.75153488</v>
+        <v>10.68950016</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1705135910841881</v>
+        <v>0.1746665578202583</v>
       </c>
       <c r="T73">
-        <v>2.102850311919286</v>
+        <v>2.172875297331183</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.219565766478359</v>
+        <v>2.18873846416616</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09256743618967234</v>
+        <v>0.09263153096493011</v>
       </c>
       <c r="C74">
-        <v>20.26157344487558</v>
+        <v>19.11786409517562</v>
       </c>
       <c r="D74">
-        <v>88.19757344487557</v>
+        <v>88.07686409517562</v>
       </c>
       <c r="E74">
-        <v>35.95599999999999</v>
+        <v>36.979</v>
       </c>
       <c r="F74">
-        <v>73.65599999999999</v>
+        <v>74.679</v>
       </c>
       <c r="G74">
         <v>5.72</v>
@@ -7343,28 +7343,28 @@
         <v>12.22</v>
       </c>
       <c r="M74">
-        <v>5.5831248</v>
+        <v>5.660668200000001</v>
       </c>
       <c r="N74">
-        <v>6.636875199999999</v>
+        <v>6.559331799999998</v>
       </c>
       <c r="O74">
-        <v>1.32737504</v>
+        <v>1.31186636</v>
       </c>
       <c r="P74">
-        <v>5.309500159999999</v>
+        <v>5.247465439999998</v>
       </c>
       <c r="Q74">
-        <v>10.68950016</v>
+        <v>10.62746544</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1746665578202583</v>
+        <v>0.1791271517219633</v>
       </c>
       <c r="T74">
-        <v>2.172875297331183</v>
+        <v>2.248087318699517</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.18873846416616</v>
+        <v>2.158755745478952</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09263153096493011</v>
+        <v>0.09269562574018789</v>
       </c>
       <c r="C75">
-        <v>19.11786409517562</v>
+        <v>17.9744847054034</v>
       </c>
       <c r="D75">
-        <v>88.07686409517562</v>
+        <v>87.9564847054034</v>
       </c>
       <c r="E75">
-        <v>36.979</v>
+        <v>38.002</v>
       </c>
       <c r="F75">
-        <v>74.679</v>
+        <v>75.702</v>
       </c>
       <c r="G75">
         <v>5.72</v>
@@ -7425,28 +7425,28 @@
         <v>12.22</v>
       </c>
       <c r="M75">
-        <v>5.660668200000001</v>
+        <v>5.738211600000001</v>
       </c>
       <c r="N75">
-        <v>6.559331799999998</v>
+        <v>6.481788399999998</v>
       </c>
       <c r="O75">
-        <v>1.31186636</v>
+        <v>1.29635768</v>
       </c>
       <c r="P75">
-        <v>5.247465439999998</v>
+        <v>5.185430719999998</v>
       </c>
       <c r="Q75">
-        <v>10.62746544</v>
+        <v>10.56543072</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1791271517219633</v>
+        <v>0.1839308682314919</v>
       </c>
       <c r="T75">
-        <v>2.248087318699517</v>
+        <v>2.329084880173109</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.158755745478952</v>
+        <v>2.129583370540047</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09269562574018789</v>
+        <v>0.09275972051544568</v>
       </c>
       <c r="C76">
-        <v>17.9744847054034</v>
+        <v>16.83143392448355</v>
       </c>
       <c r="D76">
-        <v>87.9564847054034</v>
+        <v>87.83643392448354</v>
       </c>
       <c r="E76">
-        <v>38.002</v>
+        <v>39.02499999999999</v>
       </c>
       <c r="F76">
-        <v>75.702</v>
+        <v>76.72499999999999</v>
       </c>
       <c r="G76">
         <v>5.72</v>
@@ -7507,28 +7507,28 @@
         <v>12.22</v>
       </c>
       <c r="M76">
-        <v>5.738211600000001</v>
+        <v>5.815755</v>
       </c>
       <c r="N76">
-        <v>6.481788399999998</v>
+        <v>6.404244999999999</v>
       </c>
       <c r="O76">
-        <v>1.29635768</v>
+        <v>1.280849</v>
       </c>
       <c r="P76">
-        <v>5.185430719999998</v>
+        <v>5.123395999999999</v>
       </c>
       <c r="Q76">
-        <v>10.56543072</v>
+        <v>10.503396</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1839308682314919</v>
+        <v>0.1891188820617827</v>
       </c>
       <c r="T76">
-        <v>2.329084880173109</v>
+        <v>2.416562246564587</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.129583370540047</v>
+        <v>2.101188925599514</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09275972051544568</v>
+        <v>0.09282381529070344</v>
       </c>
       <c r="C77">
-        <v>16.83143392448355</v>
+        <v>15.68871040870692</v>
       </c>
       <c r="D77">
-        <v>87.83643392448354</v>
+        <v>87.71671040870693</v>
       </c>
       <c r="E77">
-        <v>39.02499999999999</v>
+        <v>40.048</v>
       </c>
       <c r="F77">
-        <v>76.72499999999999</v>
+        <v>77.748</v>
       </c>
       <c r="G77">
         <v>5.72</v>
@@ -7589,28 +7589,28 @@
         <v>12.22</v>
       </c>
       <c r="M77">
-        <v>5.815755</v>
+        <v>5.893298400000001</v>
       </c>
       <c r="N77">
-        <v>6.404244999999999</v>
+        <v>6.326701599999998</v>
       </c>
       <c r="O77">
-        <v>1.280849</v>
+        <v>1.26534032</v>
       </c>
       <c r="P77">
-        <v>5.123395999999999</v>
+        <v>5.061361279999998</v>
       </c>
       <c r="Q77">
-        <v>10.503396</v>
+        <v>10.44136128</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1891188820617827</v>
+        <v>0.194739230377931</v>
       </c>
       <c r="T77">
-        <v>2.416562246564587</v>
+        <v>2.511329393488689</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.101188925599514</v>
+        <v>2.073541702894256</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09282381529070344</v>
+        <v>0.09288791006596121</v>
       </c>
       <c r="C78">
-        <v>15.68871040870692</v>
+        <v>14.5463128216804</v>
       </c>
       <c r="D78">
-        <v>87.71671040870693</v>
+        <v>87.5973128216804</v>
       </c>
       <c r="E78">
-        <v>40.048</v>
+        <v>41.071</v>
       </c>
       <c r="F78">
-        <v>77.748</v>
+        <v>78.771</v>
       </c>
       <c r="G78">
         <v>5.72</v>
@@ -7671,28 +7671,28 @@
         <v>12.22</v>
       </c>
       <c r="M78">
-        <v>5.893298400000001</v>
+        <v>5.970841800000001</v>
       </c>
       <c r="N78">
-        <v>6.326701599999998</v>
+        <v>6.249158199999998</v>
       </c>
       <c r="O78">
-        <v>1.26534032</v>
+        <v>1.24983164</v>
       </c>
       <c r="P78">
-        <v>5.061361279999998</v>
+        <v>4.999326559999998</v>
       </c>
       <c r="Q78">
-        <v>10.44136128</v>
+        <v>10.37932656</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.194739230377931</v>
+        <v>0.200848304634614</v>
       </c>
       <c r="T78">
-        <v>2.511329393488689</v>
+        <v>2.614337161884451</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.073541702894256</v>
+        <v>2.046612589869656</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09288791006596121</v>
+        <v>0.09295200484121899</v>
       </c>
       <c r="C79">
-        <v>14.5463128216804</v>
+        <v>13.40423983427729</v>
       </c>
       <c r="D79">
-        <v>87.5973128216804</v>
+        <v>87.47823983427729</v>
       </c>
       <c r="E79">
-        <v>41.071</v>
+        <v>42.09399999999999</v>
       </c>
       <c r="F79">
-        <v>78.771</v>
+        <v>79.794</v>
       </c>
       <c r="G79">
         <v>5.72</v>
@@ -7753,28 +7753,28 @@
         <v>12.22</v>
       </c>
       <c r="M79">
-        <v>5.970841800000001</v>
+        <v>6.0483852</v>
       </c>
       <c r="N79">
-        <v>6.249158199999998</v>
+        <v>6.171614799999999</v>
       </c>
       <c r="O79">
-        <v>1.24983164</v>
+        <v>1.23432296</v>
       </c>
       <c r="P79">
-        <v>4.999326559999998</v>
+        <v>4.937291839999999</v>
       </c>
       <c r="Q79">
-        <v>10.37932656</v>
+        <v>10.31729184</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.200848304634614</v>
+        <v>0.2075127492782681</v>
       </c>
       <c r="T79">
-        <v>2.614337161884451</v>
+        <v>2.726709272861647</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.046612589869656</v>
+        <v>2.020373966922609</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09295200484121899</v>
+        <v>0.1019904996164768</v>
       </c>
       <c r="C80">
-        <v>13.40423983427729</v>
+        <v>-1.690028780302057</v>
       </c>
       <c r="D80">
-        <v>87.47823983427729</v>
+        <v>73.40697121969795</v>
       </c>
       <c r="E80">
-        <v>42.09399999999999</v>
+        <v>43.117</v>
       </c>
       <c r="F80">
-        <v>79.794</v>
+        <v>80.81700000000001</v>
       </c>
       <c r="G80">
         <v>5.72</v>
@@ -7835,45 +7835,45 @@
         <v>12.22</v>
       </c>
       <c r="M80">
-        <v>6.0483852</v>
+        <v>7.27353</v>
       </c>
       <c r="N80">
-        <v>6.171614799999999</v>
+        <v>4.946469999999999</v>
       </c>
       <c r="O80">
-        <v>1.23432296</v>
+        <v>0.9892939999999998</v>
       </c>
       <c r="P80">
-        <v>4.937291839999999</v>
+        <v>3.957175999999999</v>
       </c>
       <c r="Q80">
-        <v>10.31729184</v>
+        <v>9.337175999999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2075127492782681</v>
+        <v>0.2148119029356036</v>
       </c>
       <c r="T80">
-        <v>2.726709272861647</v>
+        <v>2.849783489646194</v>
       </c>
       <c r="U80">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.020373966922609</v>
+        <v>1.680064562873873</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1019904996164768</v>
+        <v>0.1021681943917345</v>
       </c>
       <c r="C81">
-        <v>-1.690028780302057</v>
+        <v>-2.944436498679323</v>
       </c>
       <c r="D81">
-        <v>73.40697121969795</v>
+        <v>73.17556350132068</v>
       </c>
       <c r="E81">
-        <v>43.117</v>
+        <v>44.14</v>
       </c>
       <c r="F81">
-        <v>80.81700000000001</v>
+        <v>81.84</v>
       </c>
       <c r="G81">
         <v>5.72</v>
@@ -7917,28 +7917,28 @@
         <v>12.22</v>
       </c>
       <c r="M81">
-        <v>7.27353</v>
+        <v>7.3656</v>
       </c>
       <c r="N81">
-        <v>4.946469999999999</v>
+        <v>4.854399999999999</v>
       </c>
       <c r="O81">
-        <v>0.9892939999999998</v>
+        <v>0.9708799999999999</v>
       </c>
       <c r="P81">
-        <v>3.957175999999999</v>
+        <v>3.883519999999999</v>
       </c>
       <c r="Q81">
-        <v>9.337175999999998</v>
+        <v>9.263519999999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2148119029356036</v>
+        <v>0.2228409719586727</v>
       </c>
       <c r="T81">
-        <v>2.849783489646194</v>
+        <v>2.985165128109196</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.680064562873873</v>
+        <v>1.659063755837949</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1021681943917345</v>
+        <v>0.1023458891669923</v>
       </c>
       <c r="C82">
-        <v>-2.944436498679323</v>
+        <v>-4.197389825124105</v>
       </c>
       <c r="D82">
-        <v>73.17556350132068</v>
+        <v>72.9456101748759</v>
       </c>
       <c r="E82">
-        <v>44.14</v>
+        <v>45.163</v>
       </c>
       <c r="F82">
-        <v>81.84</v>
+        <v>82.863</v>
       </c>
       <c r="G82">
         <v>5.72</v>
@@ -7999,28 +7999,28 @@
         <v>12.22</v>
       </c>
       <c r="M82">
-        <v>7.3656</v>
+        <v>7.457669999999999</v>
       </c>
       <c r="N82">
-        <v>4.854399999999999</v>
+        <v>4.76233</v>
       </c>
       <c r="O82">
-        <v>0.9708799999999999</v>
+        <v>0.9524659999999999</v>
       </c>
       <c r="P82">
-        <v>3.883519999999999</v>
+        <v>3.809864</v>
       </c>
       <c r="Q82">
-        <v>9.263519999999998</v>
+        <v>9.189863999999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2228409719586727</v>
+        <v>0.2317152061420648</v>
       </c>
       <c r="T82">
-        <v>2.985165128109196</v>
+        <v>3.134797465357778</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.659063755837949</v>
+        <v>1.638581487247357</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1023458891669923</v>
+        <v>0.1025235839422501</v>
       </c>
       <c r="C83">
-        <v>-4.197389825124105</v>
+        <v>-5.448902427911406</v>
       </c>
       <c r="D83">
-        <v>72.9456101748759</v>
+        <v>72.7170975720886</v>
       </c>
       <c r="E83">
-        <v>45.163</v>
+        <v>46.18600000000001</v>
       </c>
       <c r="F83">
-        <v>82.863</v>
+        <v>83.88600000000001</v>
       </c>
       <c r="G83">
         <v>5.72</v>
@@ -8081,28 +8081,28 @@
         <v>12.22</v>
       </c>
       <c r="M83">
-        <v>7.457669999999999</v>
+        <v>7.549740000000001</v>
       </c>
       <c r="N83">
-        <v>4.76233</v>
+        <v>4.670259999999998</v>
       </c>
       <c r="O83">
-        <v>0.9524659999999999</v>
+        <v>0.9340519999999997</v>
       </c>
       <c r="P83">
-        <v>3.809864</v>
+        <v>3.736207999999999</v>
       </c>
       <c r="Q83">
-        <v>9.189863999999998</v>
+        <v>9.116207999999997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2317152061420648</v>
+        <v>0.2415754663458338</v>
       </c>
       <c r="T83">
-        <v>3.134797465357778</v>
+        <v>3.301055617856201</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.638581487247357</v>
+        <v>1.618598786183365</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1025235839422501</v>
+        <v>0.1027012787175079</v>
       </c>
       <c r="C84">
-        <v>-5.448902427911406</v>
+        <v>-6.69898780457963</v>
       </c>
       <c r="D84">
-        <v>72.7170975720886</v>
+        <v>72.49001219542038</v>
       </c>
       <c r="E84">
-        <v>46.18600000000001</v>
+        <v>47.209</v>
       </c>
       <c r="F84">
-        <v>83.88600000000001</v>
+        <v>84.90900000000001</v>
       </c>
       <c r="G84">
         <v>5.72</v>
@@ -8163,28 +8163,28 @@
         <v>12.22</v>
       </c>
       <c r="M84">
-        <v>7.549740000000001</v>
+        <v>7.64181</v>
       </c>
       <c r="N84">
-        <v>4.670259999999998</v>
+        <v>4.578189999999998</v>
       </c>
       <c r="O84">
-        <v>0.9340519999999997</v>
+        <v>0.9156379999999997</v>
       </c>
       <c r="P84">
-        <v>3.736207999999999</v>
+        <v>3.662551999999999</v>
       </c>
       <c r="Q84">
-        <v>9.116207999999997</v>
+        <v>9.042551999999997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2415754663458338</v>
+        <v>0.252595757161811</v>
       </c>
       <c r="T84">
-        <v>3.301055617856201</v>
+        <v>3.486873553001499</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.618598786183365</v>
+        <v>1.599097595988385</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1027012787175079</v>
+        <v>0.1028789734927656</v>
       </c>
       <c r="C85">
-        <v>-6.69898780457963</v>
+        <v>-7.947659284588468</v>
       </c>
       <c r="D85">
-        <v>72.49001219542038</v>
+        <v>72.26434071541154</v>
       </c>
       <c r="E85">
-        <v>47.209</v>
+        <v>48.232</v>
       </c>
       <c r="F85">
-        <v>84.90900000000001</v>
+        <v>85.932</v>
       </c>
       <c r="G85">
         <v>5.72</v>
@@ -8245,28 +8245,28 @@
         <v>12.22</v>
       </c>
       <c r="M85">
-        <v>7.64181</v>
+        <v>7.73388</v>
       </c>
       <c r="N85">
-        <v>4.578189999999998</v>
+        <v>4.486119999999999</v>
       </c>
       <c r="O85">
-        <v>0.9156379999999997</v>
+        <v>0.8972239999999998</v>
       </c>
       <c r="P85">
-        <v>3.662551999999999</v>
+        <v>3.588895999999999</v>
       </c>
       <c r="Q85">
-        <v>9.042551999999997</v>
+        <v>8.968895999999997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.252595757161811</v>
+        <v>0.2649935843297853</v>
       </c>
       <c r="T85">
-        <v>3.486873553001499</v>
+        <v>3.695918730039959</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.599097595988385</v>
+        <v>1.580060719845666</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1028789734927656</v>
+        <v>0.1030566682680234</v>
       </c>
       <c r="C86">
-        <v>-7.947659284588454</v>
+        <v>-9.194930031926859</v>
       </c>
       <c r="D86">
-        <v>72.26434071541154</v>
+        <v>72.04006996807314</v>
       </c>
       <c r="E86">
-        <v>48.23199999999999</v>
+        <v>49.255</v>
       </c>
       <c r="F86">
-        <v>85.93199999999999</v>
+        <v>86.955</v>
       </c>
       <c r="G86">
         <v>5.72</v>
@@ -8327,28 +8327,28 @@
         <v>12.22</v>
       </c>
       <c r="M86">
-        <v>7.733879999999998</v>
+        <v>7.82595</v>
       </c>
       <c r="N86">
-        <v>4.486120000000001</v>
+        <v>4.394049999999999</v>
       </c>
       <c r="O86">
-        <v>0.8972240000000001</v>
+        <v>0.8788099999999999</v>
       </c>
       <c r="P86">
-        <v>3.588896000000001</v>
+        <v>3.515239999999999</v>
       </c>
       <c r="Q86">
-        <v>8.968895999999999</v>
+        <v>8.895239999999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2649935843297851</v>
+        <v>0.279044455120156</v>
       </c>
       <c r="T86">
-        <v>3.695918730039956</v>
+        <v>3.93283659735021</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.580060719845666</v>
+        <v>1.561471770200423</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1030566682680234</v>
+        <v>0.1032343630432812</v>
       </c>
       <c r="C87">
-        <v>-9.194930031926859</v>
+        <v>-10.44081304767276</v>
       </c>
       <c r="D87">
-        <v>72.04006996807314</v>
+        <v>71.81718695232723</v>
       </c>
       <c r="E87">
-        <v>49.255</v>
+        <v>50.27799999999999</v>
       </c>
       <c r="F87">
-        <v>86.955</v>
+        <v>87.97799999999999</v>
       </c>
       <c r="G87">
         <v>5.72</v>
@@ -8409,28 +8409,28 @@
         <v>12.22</v>
       </c>
       <c r="M87">
-        <v>7.82595</v>
+        <v>7.918019999999999</v>
       </c>
       <c r="N87">
-        <v>4.394049999999999</v>
+        <v>4.301979999999999</v>
       </c>
       <c r="O87">
-        <v>0.8788099999999999</v>
+        <v>0.8603959999999999</v>
       </c>
       <c r="P87">
-        <v>3.515239999999999</v>
+        <v>3.441584</v>
       </c>
       <c r="Q87">
-        <v>8.895239999999998</v>
+        <v>8.821583999999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.279044455120156</v>
+        <v>0.2951025931662942</v>
       </c>
       <c r="T87">
-        <v>3.93283659735021</v>
+        <v>4.203599874276215</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.561471770200423</v>
+        <v>1.54331512170972</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1032343630432812</v>
+        <v>0.103412057818539</v>
       </c>
       <c r="C88">
-        <v>-10.44081304767276</v>
+        <v>-11.6853211725055</v>
       </c>
       <c r="D88">
-        <v>71.81718695232723</v>
+        <v>71.5956788274945</v>
       </c>
       <c r="E88">
-        <v>50.27799999999999</v>
+        <v>51.30099999999999</v>
       </c>
       <c r="F88">
-        <v>87.97799999999999</v>
+        <v>89.00099999999999</v>
       </c>
       <c r="G88">
         <v>5.72</v>
@@ -8491,28 +8491,28 @@
         <v>12.22</v>
       </c>
       <c r="M88">
-        <v>7.918019999999999</v>
+        <v>8.010089999999998</v>
       </c>
       <c r="N88">
-        <v>4.301979999999999</v>
+        <v>4.209910000000001</v>
       </c>
       <c r="O88">
-        <v>0.8603959999999999</v>
+        <v>0.8419820000000002</v>
       </c>
       <c r="P88">
-        <v>3.441584</v>
+        <v>3.367928</v>
       </c>
       <c r="Q88">
-        <v>8.821583999999998</v>
+        <v>8.747928</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2951025931662942</v>
+        <v>0.3136312139887611</v>
       </c>
       <c r="T88">
-        <v>4.203599874276215</v>
+        <v>4.516019039960065</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.54331512170972</v>
+        <v>1.525575867437195</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.103412057818539</v>
+        <v>0.1035897525937967</v>
       </c>
       <c r="C89">
-        <v>-11.6853211725055</v>
+        <v>-12.92846708917182</v>
       </c>
       <c r="D89">
-        <v>71.5956788274945</v>
+        <v>71.37553291082818</v>
       </c>
       <c r="E89">
-        <v>51.30099999999999</v>
+        <v>52.324</v>
       </c>
       <c r="F89">
-        <v>89.00099999999999</v>
+        <v>90.024</v>
       </c>
       <c r="G89">
         <v>5.72</v>
@@ -8573,28 +8573,28 @@
         <v>12.22</v>
       </c>
       <c r="M89">
-        <v>8.010089999999998</v>
+        <v>8.10216</v>
       </c>
       <c r="N89">
-        <v>4.209910000000001</v>
+        <v>4.117839999999999</v>
       </c>
       <c r="O89">
-        <v>0.8419820000000002</v>
+        <v>0.8235679999999999</v>
       </c>
       <c r="P89">
-        <v>3.367928</v>
+        <v>3.294271999999999</v>
       </c>
       <c r="Q89">
-        <v>8.747928</v>
+        <v>8.674271999999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3136312139887611</v>
+        <v>0.3352479382816395</v>
       </c>
       <c r="T89">
-        <v>4.516019039960065</v>
+        <v>4.880508066591225</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.525575867437195</v>
+        <v>1.508239778034499</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1035897525937967</v>
+        <v>0.1470920960026952</v>
       </c>
       <c r="C90">
-        <v>-12.92846708917182</v>
+        <v>-44.60541805092665</v>
       </c>
       <c r="D90">
-        <v>71.37553291082818</v>
+        <v>40.72158194907335</v>
       </c>
       <c r="E90">
-        <v>52.324</v>
+        <v>53.34699999999999</v>
       </c>
       <c r="F90">
-        <v>90.024</v>
+        <v>91.047</v>
       </c>
       <c r="G90">
         <v>5.72</v>
@@ -8655,45 +8655,45 @@
         <v>12.22</v>
       </c>
       <c r="M90">
-        <v>8.10216</v>
+        <v>13.3656996</v>
       </c>
       <c r="N90">
-        <v>4.117839999999999</v>
+        <v>-1.145699600000002</v>
       </c>
       <c r="O90">
-        <v>0.8235679999999999</v>
+        <v>-0.2291399200000004</v>
       </c>
       <c r="P90">
-        <v>3.294271999999999</v>
+        <v>-0.9165596800000018</v>
       </c>
       <c r="Q90">
-        <v>8.674271999999998</v>
+        <v>4.463440319999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3352479382816395</v>
+        <v>0.3666419462432879</v>
       </c>
       <c r="T90">
-        <v>4.880508066591225</v>
+        <v>5.409856142134845</v>
       </c>
       <c r="U90">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2</v>
+        <v>0.1828561222489244</v>
       </c>
       <c r="W90">
-        <v>0.07199999999999999</v>
+        <v>0.1199567212538579</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>1.508239778034499</v>
+        <v>0.9142806112446219</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1470920960026952</v>
+        <v>0.1481020960026952</v>
       </c>
       <c r="C91">
-        <v>-44.60541805092665</v>
+        <v>-46.03045084766896</v>
       </c>
       <c r="D91">
-        <v>40.72158194907335</v>
+        <v>40.31954915233104</v>
       </c>
       <c r="E91">
-        <v>53.34699999999999</v>
+        <v>54.36999999999999</v>
       </c>
       <c r="F91">
-        <v>91.047</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="G91">
         <v>5.72</v>
@@ -8737,37 +8737,37 @@
         <v>12.22</v>
       </c>
       <c r="M91">
-        <v>13.3656996</v>
+        <v>13.515876</v>
       </c>
       <c r="N91">
-        <v>-1.145699600000002</v>
+        <v>-1.295876000000002</v>
       </c>
       <c r="O91">
-        <v>-0.2291399200000004</v>
+        <v>-0.2591752000000003</v>
       </c>
       <c r="P91">
-        <v>-0.9165596800000018</v>
+        <v>-1.036700800000001</v>
       </c>
       <c r="Q91">
-        <v>4.463440319999997</v>
+        <v>4.343299199999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3666419462432879</v>
+        <v>0.3987261408676167</v>
       </c>
       <c r="T91">
-        <v>5.409856142134845</v>
+        <v>5.950841756348329</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1828561222489244</v>
+        <v>0.1808243875572697</v>
       </c>
       <c r="W91">
-        <v>0.1199567212538579</v>
+        <v>0.1202549799065928</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9142806112446219</v>
+        <v>0.9041219377863483</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1481020960026952</v>
+        <v>0.1491120960026952</v>
       </c>
       <c r="C92">
-        <v>-46.03045084766896</v>
+        <v>-47.44762293612212</v>
       </c>
       <c r="D92">
-        <v>40.31954915233104</v>
+        <v>39.92537706387788</v>
       </c>
       <c r="E92">
-        <v>54.36999999999999</v>
+        <v>55.393</v>
       </c>
       <c r="F92">
-        <v>92.06999999999999</v>
+        <v>93.093</v>
       </c>
       <c r="G92">
         <v>5.72</v>
@@ -8819,37 +8819,37 @@
         <v>12.22</v>
       </c>
       <c r="M92">
-        <v>13.515876</v>
+        <v>13.6660524</v>
       </c>
       <c r="N92">
-        <v>-1.295876000000002</v>
+        <v>-1.446052400000003</v>
       </c>
       <c r="O92">
-        <v>-0.2591752000000003</v>
+        <v>-0.2892104800000005</v>
       </c>
       <c r="P92">
-        <v>-1.036700800000001</v>
+        <v>-1.156841920000002</v>
       </c>
       <c r="Q92">
-        <v>4.343299199999998</v>
+        <v>4.223158079999997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3987261408676167</v>
+        <v>0.4379401565195741</v>
       </c>
       <c r="T92">
-        <v>5.950841756348329</v>
+        <v>6.612046395942589</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1808243875572697</v>
+        <v>0.1788373063753216</v>
       </c>
       <c r="W92">
-        <v>0.1202549799065928</v>
+        <v>0.1205466834241028</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9041219377863483</v>
+        <v>0.8941865318766081</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1491120960026952</v>
+        <v>0.1501220960026952</v>
       </c>
       <c r="C93">
-        <v>-47.44762293612212</v>
+        <v>-48.85716262790012</v>
       </c>
       <c r="D93">
-        <v>39.92537706387788</v>
+        <v>39.53883737209988</v>
       </c>
       <c r="E93">
-        <v>55.393</v>
+        <v>56.416</v>
       </c>
       <c r="F93">
-        <v>93.093</v>
+        <v>94.116</v>
       </c>
       <c r="G93">
         <v>5.72</v>
@@ -8901,37 +8901,37 @@
         <v>12.22</v>
       </c>
       <c r="M93">
-        <v>13.6660524</v>
+        <v>13.8162288</v>
       </c>
       <c r="N93">
-        <v>-1.446052400000003</v>
+        <v>-1.596228800000002</v>
       </c>
       <c r="O93">
-        <v>-0.2892104800000005</v>
+        <v>-0.3192457600000005</v>
       </c>
       <c r="P93">
-        <v>-1.156841920000002</v>
+        <v>-1.276983040000002</v>
       </c>
       <c r="Q93">
-        <v>4.223158079999997</v>
+        <v>4.103016959999997</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4379401565195741</v>
+        <v>0.4869576760845211</v>
       </c>
       <c r="T93">
-        <v>6.612046395942589</v>
+        <v>7.438552195435417</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1788373063753216</v>
+        <v>0.1768934226103725</v>
       </c>
       <c r="W93">
-        <v>0.1205466834241028</v>
+        <v>0.1208320455607973</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8941865318766081</v>
+        <v>0.8844671130518624</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1501220960026952</v>
+        <v>0.1511320960026952</v>
       </c>
       <c r="C94">
-        <v>-48.85716262790012</v>
+        <v>-50.2592894777522</v>
       </c>
       <c r="D94">
-        <v>39.53883737209988</v>
+        <v>39.15971052224779</v>
       </c>
       <c r="E94">
-        <v>56.416</v>
+        <v>57.43899999999999</v>
       </c>
       <c r="F94">
-        <v>94.116</v>
+        <v>95.139</v>
       </c>
       <c r="G94">
         <v>5.72</v>
@@ -8983,37 +8983,37 @@
         <v>12.22</v>
       </c>
       <c r="M94">
-        <v>13.8162288</v>
+        <v>13.9664052</v>
       </c>
       <c r="N94">
-        <v>-1.596228800000002</v>
+        <v>-1.746405200000002</v>
       </c>
       <c r="O94">
-        <v>-0.3192457600000005</v>
+        <v>-0.3492810400000004</v>
       </c>
       <c r="P94">
-        <v>-1.276983040000002</v>
+        <v>-1.397124160000001</v>
       </c>
       <c r="Q94">
-        <v>4.103016959999997</v>
+        <v>3.982875839999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4869576760845211</v>
+        <v>0.5499802012394527</v>
       </c>
       <c r="T94">
-        <v>7.438552195435417</v>
+        <v>8.501202509069048</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1768934226103725</v>
+        <v>0.1749913427973577</v>
       </c>
       <c r="W94">
-        <v>0.1208320455607973</v>
+        <v>0.1211112708773479</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8844671130518624</v>
+        <v>0.8749567139867886</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1511320960026952</v>
+        <v>0.1521420960026952</v>
       </c>
       <c r="C95">
-        <v>-50.2592894777522</v>
+        <v>-51.65421469941108</v>
       </c>
       <c r="D95">
-        <v>39.15971052224779</v>
+        <v>38.78778530058893</v>
       </c>
       <c r="E95">
-        <v>57.43899999999999</v>
+        <v>58.462</v>
       </c>
       <c r="F95">
-        <v>95.139</v>
+        <v>96.16200000000001</v>
       </c>
       <c r="G95">
         <v>5.72</v>
@@ -9065,37 +9065,37 @@
         <v>12.22</v>
       </c>
       <c r="M95">
-        <v>13.9664052</v>
+        <v>14.1165816</v>
       </c>
       <c r="N95">
-        <v>-1.746405200000002</v>
+        <v>-1.896581600000003</v>
       </c>
       <c r="O95">
-        <v>-0.3492810400000004</v>
+        <v>-0.3793163200000006</v>
       </c>
       <c r="P95">
-        <v>-1.397124160000001</v>
+        <v>-1.517265280000002</v>
       </c>
       <c r="Q95">
-        <v>3.982875839999998</v>
+        <v>3.862734719999997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5499802012394527</v>
+        <v>0.6340102347793616</v>
       </c>
       <c r="T95">
-        <v>8.501202509069048</v>
+        <v>9.918069593913891</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1749913427973577</v>
+        <v>0.1731297327675986</v>
       </c>
       <c r="W95">
-        <v>0.1211112708773479</v>
+        <v>0.1213845552297165</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8749567139867886</v>
+        <v>0.865648663837993</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1521420960026952</v>
+        <v>0.1531520960026952</v>
       </c>
       <c r="C96">
-        <v>-51.65421469941108</v>
+        <v>-53.04214155796642</v>
       </c>
       <c r="D96">
-        <v>38.78778530058893</v>
+        <v>38.42285844203359</v>
       </c>
       <c r="E96">
-        <v>58.462</v>
+        <v>59.485</v>
       </c>
       <c r="F96">
-        <v>96.16200000000001</v>
+        <v>97.185</v>
       </c>
       <c r="G96">
         <v>5.72</v>
@@ -9147,37 +9147,37 @@
         <v>12.22</v>
       </c>
       <c r="M96">
-        <v>14.1165816</v>
+        <v>14.266758</v>
       </c>
       <c r="N96">
-        <v>-1.896581600000003</v>
+        <v>-2.046758000000002</v>
       </c>
       <c r="O96">
-        <v>-0.3793163200000006</v>
+        <v>-0.4093516000000005</v>
       </c>
       <c r="P96">
-        <v>-1.517265280000002</v>
+        <v>-1.637406400000002</v>
       </c>
       <c r="Q96">
-        <v>3.862734719999997</v>
+        <v>3.742593599999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6340102347793616</v>
+        <v>0.7516522817352341</v>
       </c>
       <c r="T96">
-        <v>9.918069593913891</v>
+        <v>11.90168351269667</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1731297327675986</v>
+        <v>0.1713073145279397</v>
       </c>
       <c r="W96">
-        <v>0.1213845552297165</v>
+        <v>0.1216520862272985</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.865648663837993</v>
+        <v>0.8565365726396984</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1531520960026952</v>
+        <v>0.1541620960026952</v>
       </c>
       <c r="C97">
-        <v>-53.04214155796642</v>
+        <v>-54.4232657402957</v>
       </c>
       <c r="D97">
-        <v>38.42285844203359</v>
+        <v>38.0647342597043</v>
       </c>
       <c r="E97">
-        <v>59.485</v>
+        <v>60.508</v>
       </c>
       <c r="F97">
-        <v>97.185</v>
+        <v>98.208</v>
       </c>
       <c r="G97">
         <v>5.72</v>
@@ -9229,37 +9229,37 @@
         <v>12.22</v>
       </c>
       <c r="M97">
-        <v>14.266758</v>
+        <v>14.4169344</v>
       </c>
       <c r="N97">
-        <v>-2.046758000000002</v>
+        <v>-2.196934400000002</v>
       </c>
       <c r="O97">
-        <v>-0.4093516000000005</v>
+        <v>-0.4393868800000004</v>
       </c>
       <c r="P97">
-        <v>-1.637406400000002</v>
+        <v>-1.757547520000001</v>
       </c>
       <c r="Q97">
-        <v>3.742593599999997</v>
+        <v>3.622452479999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7516522817352341</v>
+        <v>0.9281153521690431</v>
       </c>
       <c r="T97">
-        <v>11.90168351269667</v>
+        <v>14.87710439087085</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1713073145279397</v>
+        <v>0.1695228633349403</v>
       </c>
       <c r="W97">
-        <v>0.1216520862272985</v>
+        <v>0.1219140436624308</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8565365726396984</v>
+        <v>0.8476143166747016</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1541620960026952</v>
+        <v>0.1551720960026952</v>
       </c>
       <c r="C98">
-        <v>-54.4232657402957</v>
+        <v>-55.79777570497037</v>
       </c>
       <c r="D98">
-        <v>38.0647342597043</v>
+        <v>37.71322429502963</v>
       </c>
       <c r="E98">
-        <v>60.508</v>
+        <v>61.53099999999999</v>
       </c>
       <c r="F98">
-        <v>98.208</v>
+        <v>99.23099999999999</v>
       </c>
       <c r="G98">
         <v>5.72</v>
@@ -9311,37 +9311,37 @@
         <v>12.22</v>
       </c>
       <c r="M98">
-        <v>14.4169344</v>
+        <v>14.5671108</v>
       </c>
       <c r="N98">
-        <v>-2.196934400000002</v>
+        <v>-2.347110800000001</v>
       </c>
       <c r="O98">
-        <v>-0.4393868800000004</v>
+        <v>-0.4694221600000003</v>
       </c>
       <c r="P98">
-        <v>-1.757547520000001</v>
+        <v>-1.877688640000001</v>
       </c>
       <c r="Q98">
-        <v>3.622452479999998</v>
+        <v>3.502311359999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9281153521690408</v>
+        <v>1.222220469558721</v>
       </c>
       <c r="T98">
-        <v>14.87710439087081</v>
+        <v>19.83613918782775</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1695228633349403</v>
+        <v>0.1677752049500441</v>
       </c>
       <c r="W98">
-        <v>0.1219140436624308</v>
+        <v>0.1221705999133335</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8476143166747016</v>
+        <v>0.8388760247502202</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1551720960026952</v>
+        <v>0.1561820960026952</v>
       </c>
       <c r="C99">
-        <v>-55.79777570497037</v>
+        <v>-57.165853012952</v>
       </c>
       <c r="D99">
-        <v>37.71322429502963</v>
+        <v>37.36814698704799</v>
       </c>
       <c r="E99">
-        <v>61.53099999999999</v>
+        <v>62.55399999999999</v>
       </c>
       <c r="F99">
-        <v>99.23099999999999</v>
+        <v>100.254</v>
       </c>
       <c r="G99">
         <v>5.72</v>
@@ -9393,37 +9393,37 @@
         <v>12.22</v>
       </c>
       <c r="M99">
-        <v>14.5671108</v>
+        <v>14.7172872</v>
       </c>
       <c r="N99">
-        <v>-2.347110800000001</v>
+        <v>-2.497287200000001</v>
       </c>
       <c r="O99">
-        <v>-0.4694221600000003</v>
+        <v>-0.4994574400000001</v>
       </c>
       <c r="P99">
-        <v>-1.877688640000001</v>
+        <v>-1.997829760000001</v>
       </c>
       <c r="Q99">
-        <v>3.502311359999998</v>
+        <v>3.382170239999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.222220469558721</v>
+        <v>1.810430704338082</v>
       </c>
       <c r="T99">
-        <v>19.83613918782775</v>
+        <v>29.75420878174162</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1677752049500441</v>
+        <v>0.1660632130627987</v>
       </c>
       <c r="W99">
-        <v>0.1221705999133335</v>
+        <v>0.1224219203223812</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8388760247502202</v>
+        <v>0.8303160653139934</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1561820960026952</v>
+        <v>0.1571920960026952</v>
       </c>
       <c r="C100">
-        <v>-57.165853012952</v>
+        <v>-58.52767264029796</v>
       </c>
       <c r="D100">
-        <v>37.36814698704799</v>
+        <v>37.02932735970204</v>
       </c>
       <c r="E100">
-        <v>62.55399999999999</v>
+        <v>63.577</v>
       </c>
       <c r="F100">
-        <v>100.254</v>
+        <v>101.277</v>
       </c>
       <c r="G100">
         <v>5.72</v>
@@ -9475,37 +9475,37 @@
         <v>12.22</v>
       </c>
       <c r="M100">
-        <v>14.7172872</v>
+        <v>14.8674636</v>
       </c>
       <c r="N100">
-        <v>-2.497287200000001</v>
+        <v>-2.647463600000002</v>
       </c>
       <c r="O100">
-        <v>-0.4994574400000001</v>
+        <v>-0.5294927200000004</v>
       </c>
       <c r="P100">
-        <v>-1.997829760000001</v>
+        <v>-2.117970880000001</v>
       </c>
       <c r="Q100">
-        <v>3.382170239999998</v>
+        <v>3.262029119999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.810430704338082</v>
+        <v>3.575061408676163</v>
       </c>
       <c r="T100">
-        <v>29.75420878174162</v>
+        <v>59.50841756348324</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1660632130627987</v>
+        <v>0.1643858068702452</v>
       </c>
       <c r="W100">
-        <v>0.1224219203223812</v>
+        <v>0.122668163551448</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8303160653139934</v>
+        <v>0.8219290343512258</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1571920960026952</v>
-      </c>
-      <c r="C101">
-        <v>-58.52767264029796</v>
-      </c>
-      <c r="D101">
-        <v>37.02932735970204</v>
-      </c>
-      <c r="E101">
-        <v>63.577</v>
-      </c>
-      <c r="F101">
-        <v>101.277</v>
-      </c>
-      <c r="G101">
-        <v>5.72</v>
-      </c>
-      <c r="H101">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.6</v>
-      </c>
-      <c r="K101">
-        <v>5.379999999999999</v>
-      </c>
-      <c r="L101">
-        <v>12.22</v>
-      </c>
-      <c r="M101">
-        <v>14.8674636</v>
-      </c>
-      <c r="N101">
-        <v>-2.647463600000002</v>
-      </c>
-      <c r="O101">
-        <v>-0.5294927200000004</v>
-      </c>
-      <c r="P101">
-        <v>-2.117970880000001</v>
-      </c>
-      <c r="Q101">
-        <v>3.262029119999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.575061408676163</v>
-      </c>
-      <c r="T101">
-        <v>59.50841756348324</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1643858068702452</v>
-      </c>
-      <c r="W101">
-        <v>0.122668163551448</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8219290343512258</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
